--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>702.4</v>
+        <v>708.4</v>
       </c>
       <c r="D2" s="1">
-        <v>-3.4</v>
+        <v>2.6</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0048</v>
+        <v>0.0037</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,16 +553,16 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-8.7</v>
+        <v>-2.7</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0122</v>
+        <v>-0.0038</v>
       </c>
       <c r="L2" s="1">
-        <v>-8.7</v>
+        <v>-2.7</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0122</v>
+        <v>-0.0038</v>
       </c>
       <c r="N2" s="1">
         <v>-9.9</v>
@@ -574,7 +574,7 @@
         <v>-9.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0239</v>
+        <v>0.024</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>5</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0048</v>
+        <v>0.0037</v>
       </c>
       <c r="U2" s="5">
-        <v>3.512</v>
+        <v>3.542</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0125</v>
+        <v>0.004</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0763</v>
+        <v>0.0855</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0691</v>
+        <v>0.0783</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1715</v>
+        <v>0.1815</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4407</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>844</v>
+        <v>841.6</v>
       </c>
       <c r="D3" s="1">
-        <v>-13.6</v>
+        <v>-16</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0159</v>
+        <v>-0.0187</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
+        <v>-21.3</v>
+      </c>
+      <c r="K3" s="2">
+        <v>-0.0247</v>
+      </c>
+      <c r="L3" s="1">
+        <v>-21.3</v>
+      </c>
+      <c r="M3" s="2">
+        <v>-0.0247</v>
+      </c>
+      <c r="N3" s="1">
         <v>-18.9</v>
       </c>
-      <c r="K3" s="2">
-        <v>-0.0219</v>
-      </c>
-      <c r="L3" s="1">
+      <c r="O3" s="1">
         <v>-18.9</v>
       </c>
-      <c r="M3" s="2">
-        <v>-0.0219</v>
-      </c>
-      <c r="N3" s="1">
-        <v>-18.5</v>
-      </c>
-      <c r="O3" s="1">
-        <v>-18.5</v>
-      </c>
       <c r="P3" s="1">
-        <v>-18.5</v>
+        <v>-18.9</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0287</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>5</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0159</v>
+        <v>-0.0187</v>
       </c>
       <c r="U3" s="5">
-        <v>2.11</v>
+        <v>2.104</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0223</v>
+        <v>0.0252</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0005</v>
+        <v>-0.0033</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.055</v>
+        <v>0.052</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0561</v>
+        <v>0.0531</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1024</v>
+        <v>0.0993</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>720.5</v>
+        <v>722.7</v>
       </c>
       <c r="D4" s="1">
-        <v>-13.2</v>
+        <v>-11</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,16 +719,16 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-16.6</v>
+        <v>-14.4</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0225</v>
+        <v>-0.0195</v>
       </c>
       <c r="L4" s="1">
-        <v>-16.6</v>
+        <v>-14.4</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0225</v>
+        <v>-0.0195</v>
       </c>
       <c r="N4" s="1">
         <v>-16.6</v>
@@ -749,28 +749,28 @@
         <v>5</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="U4" s="5">
-        <v>0.655</v>
+        <v>0.657</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0229</v>
+        <v>0.0198</v>
       </c>
       <c r="X4" s="2">
-        <v>0.025</v>
+        <v>0.0282</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0941</v>
+        <v>-0.0913</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1863</v>
+        <v>-0.1838</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1232</v>
+        <v>-0.1205</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>980.4</v>
+        <v>986.6</v>
       </c>
       <c r="D5" s="1">
-        <v>-7.8</v>
+        <v>-1.6</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0079</v>
+        <v>-0.0016</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,16 +802,16 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-10.9</v>
+        <v>-4.7</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.011</v>
+        <v>-0.0047</v>
       </c>
       <c r="L5" s="1">
-        <v>-10.9</v>
+        <v>-4.7</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.011</v>
+        <v>-0.0047</v>
       </c>
       <c r="N5" s="1">
         <v>-11.9</v>
@@ -823,7 +823,7 @@
         <v>-11.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0333</v>
+        <v>0.0334</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>5</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0079</v>
+        <v>-0.0016</v>
       </c>
       <c r="U5" s="5">
-        <v>4.902</v>
+        <v>4.933</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0112</v>
+        <v>0.0049</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0403</v>
+        <v>0.0469</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0495</v>
+        <v>0.0561</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0609</v>
+        <v>0.0676</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2715</v>
+        <v>0.2795</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>964.4</v>
+        <v>963.8</v>
       </c>
       <c r="D6" s="1">
-        <v>-15.1</v>
+        <v>-15.7</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0154</v>
+        <v>-0.016</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-9.3</v>
+        <v>-9.9</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0096</v>
+        <v>-0.0102</v>
       </c>
       <c r="L6" s="1">
-        <v>-9.3</v>
+        <v>-9.9</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0096</v>
+        <v>-0.0102</v>
       </c>
       <c r="N6" s="1">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="O6" s="1">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="P6" s="1">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0328</v>
+        <v>0.0326</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>5</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0154</v>
+        <v>-0.016</v>
       </c>
       <c r="U6" s="5">
-        <v>9.644</v>
+        <v>9.638</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0096</v>
+        <v>0.0103</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0367</v>
+        <v>-0.0373</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0881</v>
+        <v>-0.0886</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0602</v>
+        <v>0.0595</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3253</v>
+        <v>0.3244</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1026</v>
+        <v>0.1022</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>786.4</v>
+        <v>796.6</v>
       </c>
       <c r="D8" s="1">
-        <v>-5.8</v>
+        <v>4.4</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0073</v>
+        <v>0.0056</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-0.3</v>
+        <v>9.9</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0004</v>
+        <v>0.0126</v>
       </c>
       <c r="L8" s="1">
-        <v>-0.3</v>
+        <v>9.9</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0004</v>
+        <v>0.0126</v>
       </c>
       <c r="N8" s="1">
-        <v>0.1</v>
+        <v>-1.9</v>
       </c>
       <c r="O8" s="1">
-        <v>0.1</v>
+        <v>-1.9</v>
       </c>
       <c r="P8" s="1">
-        <v>0.1</v>
+        <v>-1.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0267</v>
+        <v>0.027</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>5</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0073</v>
+        <v>0.0056</v>
       </c>
       <c r="U8" s="5">
-        <v>3.932</v>
+        <v>3.983</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0005</v>
+        <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1076</v>
+        <v>0.122</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2043</v>
+        <v>0.2199</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2712</v>
+        <v>0.2877</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9143</v>
+        <v>0.9391</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19878.6</v>
+        <v>19966.8</v>
       </c>
       <c r="D9" s="1">
-        <v>-44.8</v>
+        <v>43.4</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0022</v>
+        <v>0.0022</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-499.04</v>
+        <v>-410.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0245</v>
+        <v>-0.0202</v>
       </c>
       <c r="L9" s="1">
-        <v>-499.04</v>
+        <v>-410.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0245</v>
+        <v>-0.0202</v>
       </c>
       <c r="N9" s="1">
-        <v>-504.64</v>
+        <v>-515.84</v>
       </c>
       <c r="O9" s="1">
-        <v>-504.64</v>
+        <v>-515.84</v>
       </c>
       <c r="P9" s="1">
-        <v>-504.64</v>
+        <v>-515.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6754</v>
+        <v>0.6759</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>5</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0022</v>
+        <v>0.0022</v>
       </c>
       <c r="U9" s="5">
-        <v>14.199</v>
+        <v>14.262</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0251</v>
+        <v>0.0205</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0084</v>
+        <v>0.0129</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0287</v>
+        <v>-0.0244</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0386</v>
+        <v>0.0432</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1813</v>
+        <v>0.1866</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>663.6</v>
+        <v>660.4</v>
       </c>
       <c r="D10" s="1">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0197</v>
+        <v>0.0148</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,16 +1217,16 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-8.5</v>
+        <v>-11.7</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0126</v>
+        <v>-0.0174</v>
       </c>
       <c r="L10" s="1">
-        <v>-8.5</v>
+        <v>-11.7</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0126</v>
+        <v>-0.0174</v>
       </c>
       <c r="N10" s="1">
         <v>-8.5</v>
@@ -1238,7 +1238,7 @@
         <v>-8.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0225</v>
+        <v>0.0224</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>5</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0197</v>
+        <v>0.0148</v>
       </c>
       <c r="U10" s="5">
-        <v>1.659</v>
+        <v>1.651</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0127</v>
+        <v>0.0176</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0215</v>
+        <v>0.0166</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.3073</v>
+        <v>0.301</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3621</v>
+        <v>0.3555</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2298</v>
+        <v>0.2239</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>865.2</v>
+        <v>865.6</v>
       </c>
       <c r="D11" s="1">
-        <v>-6.4</v>
+        <v>-6</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0073</v>
+        <v>-0.0069</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0055</v>
+        <v>0.0059</v>
       </c>
       <c r="L11" s="1">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0055</v>
+        <v>0.0059</v>
       </c>
       <c r="N11" s="1">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="O11" s="1">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="P11" s="1">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0294</v>
+        <v>0.0293</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,10 +1330,10 @@
         <v>5</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0073</v>
+        <v>-0.0069</v>
       </c>
       <c r="U11" s="5">
-        <v>2.163</v>
+        <v>2.164</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0369</v>
+        <v>0.0374</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0541</v>
+        <v>0.0546</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1918</v>
+        <v>0.1923</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2783</v>
+        <v>0.2789</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29424.1</v>
+        <v>29531.1</v>
       </c>
       <c r="D12" s="1">
-        <v>-97.3</v>
+        <v>9.7</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0033</v>
+        <v>0.0003</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-567.69</v>
+        <v>-460.69</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0189</v>
+        <v>-0.0154</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-574.99</v>
+        <v>-590.09</v>
       </c>
       <c r="O12" s="1">
-        <v>-574.99</v>
+        <v>-590.09</v>
       </c>
       <c r="P12" s="1">
-        <v>-574.99</v>
+        <v>-590.09</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>708.4</v>
+        <v>697.6</v>
       </c>
       <c r="D2" s="1">
-        <v>2.6</v>
+        <v>-8.2</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0037</v>
+        <v>-0.0116</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,16 +553,16 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-2.7</v>
+        <v>-13.5</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0038</v>
+        <v>-0.019</v>
       </c>
       <c r="L2" s="1">
-        <v>-2.7</v>
+        <v>-13.5</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0038</v>
+        <v>-0.019</v>
       </c>
       <c r="N2" s="1">
         <v>-9.9</v>
@@ -574,7 +574,7 @@
         <v>-9.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.024</v>
+        <v>0.0238</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>5</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0037</v>
+        <v>-0.0116</v>
       </c>
       <c r="U2" s="5">
-        <v>3.542</v>
+        <v>3.488</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.004</v>
+        <v>0.0195</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0855</v>
+        <v>0.0689</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0783</v>
+        <v>0.0618</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1815</v>
+        <v>0.1635</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.453</v>
+        <v>0.4309</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>841.6</v>
+        <v>835.6</v>
       </c>
       <c r="D3" s="1">
-        <v>-16</v>
+        <v>-22</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0187</v>
+        <v>-0.0257</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,16 +636,16 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-21.3</v>
+        <v>-27.3</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0247</v>
+        <v>-0.0316</v>
       </c>
       <c r="L3" s="1">
-        <v>-21.3</v>
+        <v>-27.3</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0247</v>
+        <v>-0.0316</v>
       </c>
       <c r="N3" s="1">
         <v>-18.9</v>
@@ -666,28 +666,28 @@
         <v>5</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0187</v>
+        <v>-0.0257</v>
       </c>
       <c r="U3" s="5">
-        <v>2.104</v>
+        <v>2.089</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0252</v>
+        <v>0.0326</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0033</v>
+        <v>-0.0105</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.052</v>
+        <v>0.0445</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0531</v>
+        <v>0.0456</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0993</v>
+        <v>0.0915</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>722.7</v>
+        <v>713.9</v>
       </c>
       <c r="D4" s="1">
-        <v>-11</v>
+        <v>-19.8</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.015</v>
+        <v>-0.027</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,16 +719,16 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-14.4</v>
+        <v>-23.2</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0195</v>
+        <v>-0.0315</v>
       </c>
       <c r="L4" s="1">
-        <v>-14.4</v>
+        <v>-23.2</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0195</v>
+        <v>-0.0315</v>
       </c>
       <c r="N4" s="1">
         <v>-16.6</v>
@@ -740,7 +740,7 @@
         <v>-16.6</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0245</v>
+        <v>0.0244</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>5</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.015</v>
+        <v>-0.027</v>
       </c>
       <c r="U4" s="5">
-        <v>0.657</v>
+        <v>0.649</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0198</v>
+        <v>0.0324</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0282</v>
+        <v>0.0156</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0913</v>
+        <v>-0.1024</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1838</v>
+        <v>-0.1938</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1205</v>
+        <v>-0.1312</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>986.6</v>
+        <v>975.6</v>
       </c>
       <c r="D5" s="1">
-        <v>-1.6</v>
+        <v>-12.6</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0016</v>
+        <v>-0.0128</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,16 +802,16 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-4.7</v>
+        <v>-15.7</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0047</v>
+        <v>-0.0158</v>
       </c>
       <c r="L5" s="1">
-        <v>-4.7</v>
+        <v>-15.7</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0047</v>
+        <v>-0.0158</v>
       </c>
       <c r="N5" s="1">
         <v>-11.9</v>
@@ -823,7 +823,7 @@
         <v>-11.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0334</v>
+        <v>0.0333</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>5</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0016</v>
+        <v>-0.0128</v>
       </c>
       <c r="U5" s="5">
-        <v>4.933</v>
+        <v>4.878</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0049</v>
+        <v>0.0162</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0469</v>
+        <v>0.0352</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0561</v>
+        <v>0.0443</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0676</v>
+        <v>0.0557</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2795</v>
+        <v>0.2653</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>963.8</v>
+        <v>955.4</v>
       </c>
       <c r="D6" s="1">
-        <v>-15.7</v>
+        <v>-24.1</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.016</v>
+        <v>-0.0246</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,16 +885,16 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-9.9</v>
+        <v>-18.3</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0102</v>
+        <v>-0.0188</v>
       </c>
       <c r="L6" s="1">
-        <v>-9.9</v>
+        <v>-18.3</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0102</v>
+        <v>-0.0188</v>
       </c>
       <c r="N6" s="1">
         <v>-9.9</v>
@@ -915,28 +915,28 @@
         <v>5</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.016</v>
+        <v>-0.0246</v>
       </c>
       <c r="U6" s="5">
-        <v>9.638</v>
+        <v>9.554</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0103</v>
+        <v>0.0192</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0373</v>
+        <v>-0.0457</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0886</v>
+        <v>-0.0966</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0595</v>
+        <v>0.0503</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3244</v>
+        <v>0.3129</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3018.6</v>
+        <v>3021.3</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,16 +968,16 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>-0.15</v>
+        <v>2.55</v>
       </c>
       <c r="K7" s="2">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.15</v>
+        <v>2.55</v>
       </c>
       <c r="M7" s="2">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="N7" s="1">
         <v>-0.15</v>
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1022</v>
+        <v>0.1032</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>5</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.118</v>
+        <v>1.119</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0072</v>
+        <v>0.0081</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0118</v>
+        <v>0.0127</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0188</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>796.6</v>
+        <v>794</v>
       </c>
       <c r="D8" s="1">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0056</v>
+        <v>0.0023</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,16 +1051,16 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0126</v>
+        <v>0.0093</v>
       </c>
       <c r="L8" s="1">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0126</v>
+        <v>0.0093</v>
       </c>
       <c r="N8" s="1">
         <v>-1.9</v>
@@ -1072,7 +1072,7 @@
         <v>-1.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.027</v>
+        <v>0.0271</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>5</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0056</v>
+        <v>0.0023</v>
       </c>
       <c r="U8" s="5">
-        <v>3.983</v>
+        <v>3.97</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.122</v>
+        <v>0.1183</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2199</v>
+        <v>0.216</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2877</v>
+        <v>0.2835</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9391</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19966.8</v>
+        <v>19768</v>
       </c>
       <c r="D9" s="1">
-        <v>43.4</v>
+        <v>-155.4</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,16 +1134,16 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-410.84</v>
+        <v>-609.64</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0202</v>
+        <v>-0.0299</v>
       </c>
       <c r="L9" s="1">
-        <v>-410.84</v>
+        <v>-609.64</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0202</v>
+        <v>-0.0299</v>
       </c>
       <c r="N9" s="1">
         <v>-515.84</v>
@@ -1155,7 +1155,7 @@
         <v>-515.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6759</v>
+        <v>0.6751</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>5</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="U9" s="5">
-        <v>14.262</v>
+        <v>14.12</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0205</v>
+        <v>0.0308</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0129</v>
+        <v>0.0028</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0244</v>
+        <v>-0.0341</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0432</v>
+        <v>0.0328</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1866</v>
+        <v>0.1748</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>660.4</v>
+        <v>659.6</v>
       </c>
       <c r="D10" s="1">
-        <v>9.6</v>
+        <v>8.8</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0148</v>
+        <v>0.0135</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,16 +1217,16 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-11.7</v>
+        <v>-12.5</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0174</v>
+        <v>-0.0186</v>
       </c>
       <c r="L10" s="1">
-        <v>-11.7</v>
+        <v>-12.5</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0174</v>
+        <v>-0.0186</v>
       </c>
       <c r="N10" s="1">
         <v>-8.5</v>
@@ -1238,7 +1238,7 @@
         <v>-8.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0224</v>
+        <v>0.0225</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>5</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0148</v>
+        <v>0.0135</v>
       </c>
       <c r="U10" s="5">
-        <v>1.651</v>
+        <v>1.649</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0176</v>
+        <v>0.0188</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0166</v>
+        <v>0.0153</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.301</v>
+        <v>0.2994</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3555</v>
+        <v>0.3539</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2239</v>
+        <v>0.2224</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>865.6</v>
+        <v>852.4</v>
       </c>
       <c r="D11" s="1">
-        <v>-6</v>
+        <v>-19.2</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0069</v>
+        <v>-0.022</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,16 +1300,16 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>5.1</v>
+        <v>-8.1</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0059</v>
+        <v>-0.0094</v>
       </c>
       <c r="L11" s="1">
-        <v>5.1</v>
+        <v>-8.1</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0059</v>
+        <v>-0.0094</v>
       </c>
       <c r="N11" s="1">
         <v>3.5</v>
@@ -1321,7 +1321,7 @@
         <v>3.5</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0293</v>
+        <v>0.0291</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,28 +1330,28 @@
         <v>5</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0069</v>
+        <v>-0.022</v>
       </c>
       <c r="U11" s="5">
-        <v>2.164</v>
+        <v>2.131</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v/>
+        <v>0.0094</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0374</v>
+        <v>0.0216</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0546</v>
+        <v>0.0385</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1923</v>
+        <v>0.1742</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2789</v>
+        <v>0.2594</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29531.1</v>
+        <v>29273.4</v>
       </c>
       <c r="D12" s="1">
-        <v>9.7</v>
+        <v>-248</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0003</v>
+        <v>-0.0084</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-460.69</v>
+        <v>-718.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0154</v>
+        <v>-0.024</v>
       </c>
       <c r="L12" t="str">
         <v/>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>694.6</v>
+        <v>701.8</v>
       </c>
       <c r="D2" s="1">
-        <v>-3</v>
+        <v>4.2</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0043</v>
+        <v>0.006</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-16.5</v>
+        <v>-9.3</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0232</v>
+        <v>-0.0131</v>
       </c>
       <c r="L2" s="1">
-        <v>-16.5</v>
+        <v>-9.3</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0232</v>
+        <v>-0.0131</v>
       </c>
       <c r="N2" s="1">
-        <v>-6.6</v>
+        <v>1.4</v>
       </c>
       <c r="O2" s="1">
-        <v>-16.5</v>
+        <v>-9.5</v>
       </c>
       <c r="P2" s="1">
-        <v>-16.5</v>
+        <v>-9.5</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0237</v>
+        <v>0.0238</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>6</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0043</v>
+        <v>0.006</v>
       </c>
       <c r="U2" s="5">
-        <v>3.473</v>
+        <v>3.509</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0239</v>
+        <v>0.0134</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0429</v>
+        <v>0.0537</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0572</v>
+        <v>0.0682</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1559</v>
+        <v>0.1679</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4459</v>
+        <v>0.4608</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>830.4</v>
+        <v>839.6</v>
       </c>
       <c r="D3" s="1">
-        <v>-5.2</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0062</v>
+        <v>0.0048</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-32.5</v>
+        <v>-23.3</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0377</v>
+        <v>-0.027</v>
       </c>
       <c r="L3" s="1">
-        <v>-32.5</v>
+        <v>-23.3</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0377</v>
+        <v>-0.027</v>
       </c>
       <c r="N3" s="1">
-        <v>-13.6</v>
+        <v>-4</v>
       </c>
       <c r="O3" s="1">
-        <v>-32.5</v>
+        <v>-23.3</v>
       </c>
       <c r="P3" s="1">
-        <v>-32.5</v>
+        <v>-23.3</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0283</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>6</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0062</v>
+        <v>0.0048</v>
       </c>
       <c r="U3" s="5">
-        <v>2.076</v>
+        <v>2.099</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.039</v>
+        <v>0.0276</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0086</v>
+        <v>0.0024</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.038</v>
+        <v>0.0495</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0549</v>
+        <v>0.0666</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0898</v>
+        <v>0.1018</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>707.3</v>
+        <v>702.9</v>
       </c>
       <c r="D4" s="1">
-        <v>-6.6</v>
+        <v>-11</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0092</v>
+        <v>-0.0154</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-29.8</v>
+        <v>-34.2</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0404</v>
+        <v>-0.0464</v>
       </c>
       <c r="L4" s="1">
-        <v>-29.8</v>
+        <v>-34.2</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0404</v>
+        <v>-0.0464</v>
       </c>
       <c r="N4" s="1">
-        <v>-13.2</v>
+        <v>-17.6</v>
       </c>
       <c r="O4" s="1">
-        <v>-29.8</v>
+        <v>-32</v>
       </c>
       <c r="P4" s="1">
-        <v>-29.8</v>
+        <v>-32</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0241</v>
+        <v>0.0238</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>6</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0092</v>
+        <v>-0.0154</v>
       </c>
       <c r="U4" s="5">
-        <v>0.643</v>
+        <v>0.639</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.042</v>
+        <v>0.0485</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0287</v>
+        <v>-0.0347</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1107</v>
+        <v>-0.1162</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1902</v>
+        <v>-0.1952</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1204</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D5" s="1">
-        <v>-4.6</v>
+        <v>-1.6</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0047</v>
+        <v>-0.0016</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-20.3</v>
+        <v>-17.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0205</v>
+        <v>-0.0175</v>
       </c>
       <c r="L5" s="1">
-        <v>-20.3</v>
+        <v>-17.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0205</v>
+        <v>-0.0175</v>
       </c>
       <c r="N5" s="1">
-        <v>-8.4</v>
+        <v>-5.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-20.3</v>
+        <v>-17.5</v>
       </c>
       <c r="P5" s="1">
-        <v>-20.3</v>
+        <v>-17.5</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0331</v>
+        <v>0.033</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>6</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0047</v>
+        <v>-0.0016</v>
       </c>
       <c r="U5" s="5">
-        <v>4.855</v>
+        <v>4.87</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.021</v>
+        <v>0.0179</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0244</v>
+        <v>0.0276</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0394</v>
+        <v>0.0426</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0576</v>
+        <v>0.0609</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.277</v>
+        <v>0.2809</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>944</v>
+        <v>950.7</v>
       </c>
       <c r="D6" s="1">
-        <v>-11.4</v>
+        <v>-4.7</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0119</v>
+        <v>-0.0049</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-29.7</v>
+        <v>-23</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0305</v>
+        <v>-0.0236</v>
       </c>
       <c r="L6" s="1">
-        <v>-29.7</v>
+        <v>-23</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0305</v>
+        <v>-0.0236</v>
       </c>
       <c r="N6" s="1">
-        <v>-19.8</v>
+        <v>-12.9</v>
       </c>
       <c r="O6" s="1">
-        <v>-29.7</v>
+        <v>-23</v>
       </c>
       <c r="P6" s="1">
-        <v>-29.7</v>
+        <v>-23</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0322</v>
@@ -915,28 +915,28 @@
         <v>6</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0119</v>
+        <v>-0.0049</v>
       </c>
       <c r="U6" s="5">
-        <v>9.44</v>
+        <v>9.507</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0315</v>
+        <v>0.0242</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0588</v>
+        <v>-0.0521</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1073</v>
+        <v>-0.1009</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0629</v>
+        <v>0.0704</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3153</v>
+        <v>0.3247</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3021.3</v>
+        <v>3015.9</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>-5.4</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>-0.0018</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,28 +968,28 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>2.55</v>
+        <v>-2.85</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0008</v>
+        <v>-0.0009</v>
       </c>
       <c r="L7" s="1">
-        <v>2.55</v>
+        <v>-2.85</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0008</v>
+        <v>-0.0009</v>
       </c>
       <c r="N7" s="1">
-        <v>2.7</v>
+        <v>-2.7</v>
       </c>
       <c r="O7" s="1">
-        <v>2.55</v>
+        <v>-2.85</v>
       </c>
       <c r="P7" s="1">
-        <v>2.55</v>
+        <v>-2.85</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1029</v>
+        <v>0.1023</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,28 +998,28 @@
         <v>6</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>-0.0018</v>
       </c>
       <c r="U7" s="5">
-        <v>1.119</v>
+        <v>1.117</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
       </c>
       <c r="W7" s="2">
-        <v/>
+        <v>0.0009</v>
       </c>
       <c r="X7" s="2">
-        <v>0.0018</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0081</v>
+        <v>0.0063</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0127</v>
+        <v>0.0109</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0216</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>782.4</v>
+        <v>791.8</v>
       </c>
       <c r="D8" s="1">
-        <v>-11.6</v>
+        <v>-2.2</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0146</v>
+        <v>-0.0028</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-4.3</v>
+        <v>5.1</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0055</v>
+        <v>0.0065</v>
       </c>
       <c r="L8" s="1">
-        <v>-4.3</v>
+        <v>5.1</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0055</v>
+        <v>0.0065</v>
       </c>
       <c r="N8" s="1">
-        <v>-2.4</v>
+        <v>7</v>
       </c>
       <c r="O8" s="1">
-        <v>-4.3</v>
+        <v>3.5</v>
       </c>
       <c r="P8" s="1">
-        <v>-4.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0267</v>
+        <v>0.0269</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>6</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0146</v>
+        <v>-0.0028</v>
       </c>
       <c r="U8" s="5">
-        <v>3.912</v>
+        <v>3.959</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0056</v>
+        <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0659</v>
+        <v>0.0787</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1981</v>
+        <v>0.2125</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2685</v>
+        <v>0.2837</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9482</v>
+        <v>0.9716</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19754</v>
+        <v>19852</v>
       </c>
       <c r="D9" s="1">
-        <v>-14</v>
+        <v>84</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0007</v>
+        <v>0.0042</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-623.64</v>
+        <v>-525.64</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0306</v>
+        <v>-0.0258</v>
       </c>
       <c r="L9" s="1">
-        <v>-623.64</v>
+        <v>-525.64</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0306</v>
+        <v>-0.0258</v>
       </c>
       <c r="N9" s="1">
-        <v>-107.8</v>
+        <v>-15.4</v>
       </c>
       <c r="O9" s="1">
-        <v>-623.64</v>
+        <v>-531.24</v>
       </c>
       <c r="P9" s="1">
-        <v>-623.64</v>
+        <v>-531.24</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6729</v>
+        <v>0.6732</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>6</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0007</v>
+        <v>0.0042</v>
       </c>
       <c r="U9" s="5">
-        <v>14.11</v>
+        <v>14.18</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0315</v>
+        <v>0.0264</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.016</v>
+        <v>-0.0111</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0348</v>
+        <v>-0.03</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0334</v>
+        <v>0.0385</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1767</v>
+        <v>0.1825</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>670</v>
+        <v>672.8</v>
       </c>
       <c r="D10" s="1">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0158</v>
+        <v>0.02</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-2.1</v>
+        <v>0.7</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0031</v>
+        <v>0.001</v>
       </c>
       <c r="L10" s="1">
-        <v>-2.1</v>
+        <v>0.7</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0031</v>
+        <v>0.001</v>
       </c>
       <c r="N10" s="1">
-        <v>6.4</v>
+        <v>8.8</v>
       </c>
       <c r="O10" s="1">
-        <v>-2.1</v>
+        <v>0.3</v>
       </c>
       <c r="P10" s="1">
-        <v>-2.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0228</v>
@@ -1247,28 +1247,28 @@
         <v>6</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0158</v>
+        <v>0.02</v>
       </c>
       <c r="U10" s="5">
-        <v>1.675</v>
+        <v>1.682</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.003</v>
+        <v/>
       </c>
       <c r="X10" s="2">
-        <v>0.0091</v>
+        <v>0.0133</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.3199</v>
+        <v>0.3254</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3843</v>
+        <v>0.3901</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2767</v>
+        <v>0.2821</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>845.6</v>
+        <v>850</v>
       </c>
       <c r="D11" s="1">
-        <v>-6.8</v>
+        <v>-2.4</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.008</v>
+        <v>-0.0028</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-14.9</v>
+        <v>-10.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0173</v>
+        <v>-0.0122</v>
       </c>
       <c r="L11" s="1">
-        <v>-14.9</v>
+        <v>-10.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0173</v>
+        <v>-0.0122</v>
       </c>
       <c r="N11" s="1">
-        <v>-18.4</v>
+        <v>-14</v>
       </c>
       <c r="O11" s="1">
-        <v>-14.9</v>
+        <v>-10.5</v>
       </c>
       <c r="P11" s="1">
-        <v>-14.9</v>
+        <v>-10.5</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0288</v>
@@ -1330,28 +1330,28 @@
         <v>6</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.008</v>
+        <v>-0.0028</v>
       </c>
       <c r="U11" s="5">
-        <v>2.114</v>
+        <v>2.125</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0175</v>
+        <v>0.0122</v>
       </c>
       <c r="X11" s="2">
-        <v>-0.0009</v>
+        <v>0.0043</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0302</v>
+        <v>0.0356</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1699</v>
+        <v>0.176</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2599</v>
+        <v>0.2664</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29220.6</v>
+        <v>29351.5</v>
       </c>
       <c r="D12" s="1">
-        <v>-52.8</v>
+        <v>78.1</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-771.19</v>
+        <v>-640.29</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0257</v>
+        <v>-0.0213</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-181.1</v>
+        <v>-54.8</v>
       </c>
       <c r="O12" s="1">
-        <v>-771.19</v>
+        <v>-646.09</v>
       </c>
       <c r="P12" s="1">
-        <v>-771.19</v>
+        <v>-646.09</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9954</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>702.4</v>
+        <v>708.4</v>
       </c>
       <c r="D2" s="1">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0026</v>
+        <v>0.0111</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-8.7</v>
+        <v>-2.7</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0122</v>
+        <v>-0.0038</v>
       </c>
       <c r="L2" s="1">
-        <v>-8.7</v>
+        <v>-2.7</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0122</v>
+        <v>-0.0038</v>
       </c>
       <c r="N2" s="1">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="O2" s="1">
-        <v>-9.5</v>
+        <v>-2.7</v>
       </c>
       <c r="P2" s="1">
-        <v>-9.5</v>
+        <v>-2.7</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0238</v>
@@ -583,28 +583,28 @@
         <v>7</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0026</v>
+        <v>0.0111</v>
       </c>
       <c r="U2" s="5">
-        <v>3.512</v>
+        <v>3.542</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0125</v>
+        <v>0.004</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0547</v>
+        <v>0.0637</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0691</v>
+        <v>0.0783</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1781</v>
+        <v>0.1882</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.462</v>
+        <v>0.4745</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>849.6</v>
+        <v>848.8</v>
       </c>
       <c r="D3" s="1">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0153</v>
+        <v>0.0143</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-13.3</v>
+        <v>-14.1</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0154</v>
+        <v>-0.0163</v>
       </c>
       <c r="L3" s="1">
-        <v>-13.3</v>
+        <v>-14.1</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0154</v>
+        <v>-0.0163</v>
       </c>
       <c r="N3" s="1">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-13.7</v>
+        <v>-14.1</v>
       </c>
       <c r="P3" s="1">
-        <v>-13.7</v>
+        <v>-14.1</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0288</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>7</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0153</v>
+        <v>0.0143</v>
       </c>
       <c r="U3" s="5">
-        <v>2.124</v>
+        <v>2.122</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0155</v>
+        <v>0.0165</v>
       </c>
       <c r="X3" s="2">
-        <v>0.0143</v>
+        <v>0.0133</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0536</v>
+        <v>0.0526</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.115</v>
+        <v>0.1139</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>704</v>
+        <v>702.9</v>
       </c>
       <c r="D4" s="1">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0047</v>
+        <v>0.0031</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-33.1</v>
+        <v>-34.2</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0449</v>
+        <v>-0.0464</v>
       </c>
       <c r="L4" s="1">
-        <v>-33.1</v>
+        <v>-34.2</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0449</v>
+        <v>-0.0464</v>
       </c>
       <c r="N4" s="1">
-        <v>-15.4</v>
+        <v>-17.6</v>
       </c>
       <c r="O4" s="1">
-        <v>-30.9</v>
+        <v>-34.2</v>
       </c>
       <c r="P4" s="1">
-        <v>-30.9</v>
+        <v>-34.2</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0239</v>
+        <v>0.0236</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>7</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0047</v>
+        <v>0.0031</v>
       </c>
       <c r="U4" s="5">
-        <v>0.64</v>
+        <v>0.639</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0469</v>
+        <v>0.0485</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0333</v>
+        <v>-0.0348</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1148</v>
+        <v>-0.1161</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1784</v>
+        <v>-0.1797</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1245</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>966.8</v>
+        <v>973.8</v>
       </c>
       <c r="D5" s="1">
-        <v>-3.6</v>
+        <v>3.4</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-24.5</v>
+        <v>-17.5</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0247</v>
+        <v>-0.0177</v>
       </c>
       <c r="L5" s="1">
-        <v>-24.5</v>
+        <v>-17.5</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0247</v>
+        <v>-0.0177</v>
       </c>
       <c r="N5" s="1">
-        <v>-12.6</v>
+        <v>-5.6</v>
       </c>
       <c r="O5" s="1">
-        <v>-23.9</v>
+        <v>-17.5</v>
       </c>
       <c r="P5" s="1">
-        <v>-23.9</v>
+        <v>-17.5</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0328</v>
+        <v>0.0327</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>7</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="U5" s="5">
-        <v>4.834</v>
+        <v>4.869</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0254</v>
+        <v>0.0181</v>
       </c>
       <c r="X5" s="2">
-        <v>0.02</v>
+        <v>0.0274</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0348</v>
+        <v>0.0423</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0591</v>
+        <v>0.0667</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2714</v>
+        <v>0.2806</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>955.4</v>
+        <v>951.5</v>
       </c>
       <c r="D6" s="1">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0043</v>
+        <v>0.0002</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-18.3</v>
+        <v>-22.2</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0188</v>
+        <v>-0.0228</v>
       </c>
       <c r="L6" s="1">
-        <v>-18.3</v>
+        <v>-22.2</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0188</v>
+        <v>-0.0228</v>
       </c>
       <c r="N6" s="1">
-        <v>-8.4</v>
+        <v>-12.3</v>
       </c>
       <c r="O6" s="1">
-        <v>-18.3</v>
+        <v>-22.2</v>
       </c>
       <c r="P6" s="1">
-        <v>-18.3</v>
+        <v>-22.2</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0324</v>
+        <v>0.032</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>7</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0043</v>
+        <v>0.0002</v>
       </c>
       <c r="U6" s="5">
-        <v>9.554</v>
+        <v>9.515</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0192</v>
+        <v>0.0233</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0474</v>
+        <v>-0.0513</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0965</v>
+        <v>-0.1002</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0886</v>
+        <v>0.0841</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3312</v>
+        <v>0.3258</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3018.6</v>
+        <v>3024</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,28 +968,28 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>-0.15</v>
+        <v>5.25</v>
       </c>
       <c r="K7" s="2">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.15</v>
+        <v>5.25</v>
       </c>
       <c r="M7" s="2">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O7" s="1">
-        <v>-0.15</v>
+        <v>5.25</v>
       </c>
       <c r="P7" s="1">
-        <v>-0.15</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1023</v>
+        <v>0.1016</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>7</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="U7" s="5">
-        <v>1.118</v>
+        <v>1.12</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0009</v>
+        <v>0.0027</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0072</v>
+        <v>0.009</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0099</v>
+        <v>0.0117</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0207</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>778.4</v>
+        <v>784.4</v>
       </c>
       <c r="D8" s="1">
-        <v>-6.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0079</v>
+        <v>-0.0003</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-8.3</v>
+        <v>-2.3</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0105</v>
+        <v>-0.0029</v>
       </c>
       <c r="L8" s="1">
-        <v>-8.3</v>
+        <v>-2.3</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0105</v>
+        <v>-0.0029</v>
       </c>
       <c r="N8" s="1">
-        <v>-6.8</v>
+        <v>-0.4</v>
       </c>
       <c r="O8" s="1">
-        <v>-8.7</v>
+        <v>-2.3</v>
       </c>
       <c r="P8" s="1">
-        <v>-8.7</v>
+        <v>-2.3</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0264</v>
@@ -1081,28 +1081,28 @@
         <v>7</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0079</v>
+        <v>-0.0003</v>
       </c>
       <c r="U8" s="5">
-        <v>3.892</v>
+        <v>3.922</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0108</v>
+        <v>0.0031</v>
       </c>
       <c r="X8" s="2">
-        <v>0.0605</v>
+        <v>0.0686</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.192</v>
+        <v>0.2012</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2756</v>
+        <v>0.2855</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9383</v>
+        <v>0.9532</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19835.2</v>
+        <v>20091.4</v>
       </c>
       <c r="D9" s="1">
-        <v>78.4</v>
+        <v>334.6</v>
       </c>
       <c r="E9" s="2">
-        <v>0.004</v>
+        <v>0.0169</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-542.44</v>
+        <v>-286.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0266</v>
+        <v>-0.014</v>
       </c>
       <c r="L9" s="1">
-        <v>-542.44</v>
+        <v>-286.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0266</v>
+        <v>-0.014</v>
       </c>
       <c r="N9" s="1">
-        <v>-19.6</v>
+        <v>229.6</v>
       </c>
       <c r="O9" s="1">
-        <v>-534.04</v>
+        <v>-286.24</v>
       </c>
       <c r="P9" s="1">
-        <v>-534.04</v>
+        <v>-286.24</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6725</v>
+        <v>0.6749</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>7</v>
       </c>
       <c r="T9" s="2">
-        <v>0.004</v>
+        <v>0.0169</v>
       </c>
       <c r="U9" s="5">
-        <v>14.168</v>
+        <v>14.351</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0273</v>
+        <v>0.0142</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0119</v>
+        <v>0.0009</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0309</v>
+        <v>-0.0184</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0415</v>
+        <v>0.055</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1815</v>
+        <v>0.1967</v>
       </c>
     </row>
     <row r="10">
@@ -1232,13 +1232,13 @@
         <v>2</v>
       </c>
       <c r="O10" s="1">
-        <v>-6.9</v>
+        <v>-6.5</v>
       </c>
       <c r="P10" s="1">
-        <v>-6.9</v>
+        <v>-6.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0226</v>
+        <v>0.0224</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>856.4</v>
+        <v>854</v>
       </c>
       <c r="D11" s="1">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0042</v>
+        <v>0.0014</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-4.1</v>
+        <v>-6.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0048</v>
+        <v>-0.0076</v>
       </c>
       <c r="L11" s="1">
-        <v>-4.1</v>
+        <v>-6.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0048</v>
+        <v>-0.0076</v>
       </c>
       <c r="N11" s="1">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="O11" s="1">
-        <v>-4.5</v>
+        <v>-6.5</v>
       </c>
       <c r="P11" s="1">
-        <v>-4.5</v>
+        <v>-6.5</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.029</v>
+        <v>0.0287</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,28 +1330,28 @@
         <v>7</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0042</v>
+        <v>0.0014</v>
       </c>
       <c r="U11" s="5">
-        <v>2.141</v>
+        <v>2.135</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0047</v>
+        <v>0.0075</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0119</v>
+        <v>0.009</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0434</v>
+        <v>0.0405</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1974</v>
+        <v>0.1941</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.276</v>
+        <v>0.2724</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29332.4</v>
+        <v>29604.8</v>
       </c>
       <c r="D12" s="1">
-        <v>85.8</v>
+        <v>358.2</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0029</v>
+        <v>0.0122</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-659.39</v>
+        <v>-386.99</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.022</v>
+        <v>-0.0129</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-62.8</v>
+        <v>203.1</v>
       </c>
       <c r="O12" s="1">
-        <v>-650.59</v>
+        <v>-386.99</v>
       </c>
       <c r="P12" s="1">
-        <v>-650.59</v>
+        <v>-386.99</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9945</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>703.4</v>
+        <v>709</v>
       </c>
       <c r="D2" s="1">
-        <v>-5</v>
+        <v>0.6</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0071</v>
+        <v>0.0008</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-7.7</v>
+        <v>-2.1</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0108</v>
+        <v>-0.003</v>
       </c>
       <c r="L2" s="1">
-        <v>-7.7</v>
+        <v>-2.1</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0108</v>
+        <v>-0.003</v>
       </c>
       <c r="N2" s="1">
-        <v>2.2</v>
+        <v>11.4</v>
       </c>
       <c r="O2" s="1">
-        <v>-7.7</v>
+        <v>-2.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-7.7</v>
+        <v>-2.1</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0238</v>
+        <v>0.024</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>8</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0071</v>
+        <v>0.0008</v>
       </c>
       <c r="U2" s="5">
-        <v>3.517</v>
+        <v>3.545</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0111</v>
+        <v>0.0031</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0562</v>
+        <v>0.0646</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0706</v>
+        <v>0.0791</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1901</v>
+        <v>0.1996</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4575</v>
+        <v>0.4691</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>848</v>
+        <v>841.2</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.8</v>
+        <v>-7.6</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0009</v>
+        <v>-0.009</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0173</v>
+        <v>-0.0252</v>
       </c>
       <c r="L3" s="1">
-        <v>-14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0173</v>
+        <v>-0.0252</v>
       </c>
       <c r="N3" s="1">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="O3" s="1">
-        <v>-14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="P3" s="1">
-        <v>-14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0287</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>8</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0009</v>
+        <v>-0.009</v>
       </c>
       <c r="U3" s="5">
-        <v>2.12</v>
+        <v>2.103</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0175</v>
+        <v>0.0257</v>
       </c>
       <c r="X3" s="2">
-        <v>0.0124</v>
+        <v>0.0043</v>
       </c>
       <c r="Y3" s="2">
+        <v>0.0515</v>
+      </c>
+      <c r="Z3" s="2">
         <v>0.06</v>
       </c>
-      <c r="Z3" s="2">
-        <v>0.0686</v>
-      </c>
       <c r="AA3" s="2">
-        <v>0.1169</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>699.6</v>
+        <v>704</v>
       </c>
       <c r="D4" s="1">
-        <v>-3.3</v>
+        <v>1.1</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0047</v>
+        <v>0.0016</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-37.5</v>
+        <v>-33.1</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0509</v>
+        <v>-0.0449</v>
       </c>
       <c r="L4" s="1">
-        <v>-37.5</v>
+        <v>-33.1</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0509</v>
+        <v>-0.0449</v>
       </c>
       <c r="N4" s="1">
-        <v>-20.9</v>
+        <v>-9.9</v>
       </c>
       <c r="O4" s="1">
-        <v>-37.5</v>
+        <v>-33.1</v>
       </c>
       <c r="P4" s="1">
-        <v>-37.5</v>
+        <v>-33.1</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0237</v>
+        <v>0.0239</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>8</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0047</v>
+        <v>0.0016</v>
       </c>
       <c r="U4" s="5">
-        <v>0.636</v>
+        <v>0.64</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0535</v>
+        <v>0.0469</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0392</v>
+        <v>-0.0332</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1203</v>
+        <v>-0.1148</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1783</v>
+        <v>-0.1731</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1276</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>969</v>
+        <v>974.2</v>
       </c>
       <c r="D5" s="1">
-        <v>-4.8</v>
+        <v>0.4</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0049</v>
+        <v>0.0004</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-22.3</v>
+        <v>-17.1</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0225</v>
+        <v>-0.0172</v>
       </c>
       <c r="L5" s="1">
-        <v>-22.3</v>
+        <v>-17.1</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0225</v>
+        <v>-0.0172</v>
       </c>
       <c r="N5" s="1">
-        <v>-10.4</v>
+        <v>-1.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-22.3</v>
+        <v>-17.1</v>
       </c>
       <c r="P5" s="1">
-        <v>-22.3</v>
+        <v>-17.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0328</v>
+        <v>0.033</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>8</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0049</v>
+        <v>0.0004</v>
       </c>
       <c r="U5" s="5">
-        <v>4.845</v>
+        <v>4.871</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0231</v>
+        <v>0.0177</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0223</v>
+        <v>0.0278</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0373</v>
+        <v>0.0428</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0583</v>
+        <v>0.0639</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2762</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>940</v>
+        <v>936.7</v>
       </c>
       <c r="D6" s="1">
-        <v>-11.5</v>
+        <v>-14.8</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0121</v>
+        <v>-0.0156</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-33.7</v>
+        <v>-37</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0346</v>
+        <v>-0.038</v>
       </c>
       <c r="L6" s="1">
-        <v>-33.7</v>
+        <v>-37</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0346</v>
+        <v>-0.038</v>
       </c>
       <c r="N6" s="1">
-        <v>-23.8</v>
+        <v>-18.7</v>
       </c>
       <c r="O6" s="1">
-        <v>-33.7</v>
+        <v>-37</v>
       </c>
       <c r="P6" s="1">
-        <v>-33.7</v>
+        <v>-37</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0318</v>
@@ -915,28 +915,28 @@
         <v>8</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0121</v>
+        <v>-0.0156</v>
       </c>
       <c r="U6" s="5">
-        <v>9.4</v>
+        <v>9.367</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0359</v>
+        <v>0.0395</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0628</v>
+        <v>-0.0661</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1111</v>
+        <v>-0.1142</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0499</v>
+        <v>0.0462</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3016</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="7">
@@ -947,46 +947,46 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3024</v>
+        <v>3018.6</v>
       </c>
       <c r="D7" s="1">
+        <v>-5.4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-0.0018</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v/>
+      </c>
+      <c r="H7" s="1">
+        <v/>
+      </c>
+      <c r="I7" s="2">
+        <v/>
+      </c>
+      <c r="J7" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="2">
+      <c r="L7" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="M7" s="2">
         <v>0</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="2">
-        <v/>
-      </c>
-      <c r="H7" s="1">
-        <v/>
-      </c>
-      <c r="I7" s="2">
-        <v/>
-      </c>
-      <c r="J7" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.0017</v>
-      </c>
-      <c r="L7" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.0017</v>
-      </c>
       <c r="N7" s="1">
-        <v>5.4</v>
+        <v>-2.7</v>
       </c>
       <c r="O7" s="1">
-        <v>5.25</v>
+        <v>-0.15</v>
       </c>
       <c r="P7" s="1">
-        <v>5.25</v>
+        <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
         <v>0.1024</v>
@@ -998,10 +998,10 @@
         <v>8</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>-0.0018</v>
       </c>
       <c r="U7" s="5">
-        <v>1.12</v>
+        <v>1.118</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0027</v>
+        <v>0.0009</v>
       </c>
       <c r="Y7" s="2">
+        <v>0.0072</v>
+      </c>
+      <c r="Z7" s="2">
         <v>0.009</v>
       </c>
-      <c r="Z7" s="2">
-        <v>0.0108</v>
-      </c>
       <c r="AA7" s="2">
-        <v>0.0206</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>779</v>
+        <v>786.4</v>
       </c>
       <c r="D8" s="1">
-        <v>-5.4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0069</v>
+        <v>0.0025</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-7.7</v>
+        <v>-0.3</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0098</v>
+        <v>-0.0004</v>
       </c>
       <c r="L8" s="1">
-        <v>-7.7</v>
+        <v>-0.3</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0098</v>
+        <v>-0.0004</v>
       </c>
       <c r="N8" s="1">
-        <v>-5.8</v>
+        <v>-7.6</v>
       </c>
       <c r="O8" s="1">
-        <v>-7.7</v>
+        <v>-0.3</v>
       </c>
       <c r="P8" s="1">
-        <v>-7.7</v>
+        <v>-0.3</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0264</v>
+        <v>0.0267</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>8</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0069</v>
+        <v>0.0025</v>
       </c>
       <c r="U8" s="5">
-        <v>3.895</v>
+        <v>3.932</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.01</v>
+        <v>0.0005</v>
       </c>
       <c r="X8" s="2">
-        <v>0.0613</v>
+        <v>0.0714</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1929</v>
+        <v>0.2043</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2742</v>
+        <v>0.2863</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9455</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20048</v>
+        <v>19985</v>
       </c>
       <c r="D9" s="1">
-        <v>-43.4</v>
+        <v>-106.4</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0022</v>
+        <v>-0.0053</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-329.64</v>
+        <v>-392.64</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0162</v>
+        <v>-0.0193</v>
       </c>
       <c r="L9" s="1">
-        <v>-329.64</v>
+        <v>-392.64</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0162</v>
+        <v>-0.0193</v>
       </c>
       <c r="N9" s="1">
-        <v>186.2</v>
+        <v>217</v>
       </c>
       <c r="O9" s="1">
-        <v>-329.64</v>
+        <v>-392.64</v>
       </c>
       <c r="P9" s="1">
-        <v>-329.64</v>
+        <v>-392.64</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.679</v>
+        <v>0.6778</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>8</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0022</v>
+        <v>-0.0053</v>
       </c>
       <c r="U9" s="5">
-        <v>14.32</v>
+        <v>14.275</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0164</v>
+        <v>0.0196</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0014</v>
+        <v>-0.0045</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0204</v>
+        <v>-0.0235</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0508</v>
+        <v>0.0475</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1941</v>
+        <v>0.1904</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D10" s="1">
-        <v>2.4</v>
+        <v>-1.6</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0036</v>
+        <v>-0.0024</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0061</v>
+        <v>-0.0121</v>
       </c>
       <c r="L10" s="1">
-        <v>-4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0061</v>
+        <v>-0.0121</v>
       </c>
       <c r="N10" s="1">
         <v>4.4</v>
       </c>
       <c r="O10" s="1">
-        <v>-4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0226</v>
+        <v>0.0225</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>8</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0036</v>
+        <v>-0.0024</v>
       </c>
       <c r="U10" s="5">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="X10" s="2">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.316</v>
+        <v>0.3081</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3859</v>
+        <v>0.3776</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2748</v>
+        <v>0.2671</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="D11" s="1">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.007</v>
+        <v>0.0047</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0145</v>
+        <v>-0.0029</v>
       </c>
       <c r="L11" s="1">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0145</v>
+        <v>-0.0029</v>
       </c>
       <c r="N11" s="1">
-        <v>-16</v>
+        <v>5.6</v>
       </c>
       <c r="O11" s="1">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="P11" s="1">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0287</v>
+        <v>0.0291</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,28 +1330,28 @@
         <v>8</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.007</v>
+        <v>0.0047</v>
       </c>
       <c r="U11" s="5">
-        <v>2.12</v>
+        <v>2.145</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0146</v>
+        <v>0.0028</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0019</v>
+        <v>0.0137</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0331</v>
+        <v>0.0453</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1772</v>
+        <v>0.1911</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2672</v>
+        <v>0.2822</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29527</v>
+        <v>29477.1</v>
       </c>
       <c r="D12" s="1">
-        <v>-77.8</v>
+        <v>-127.7</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0026</v>
+        <v>-0.0043</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-464.79</v>
+        <v>-514.69</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0155</v>
+        <v>-0.0172</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,16 +1395,16 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>125.3</v>
+        <v>203.7</v>
       </c>
       <c r="O12" s="1">
-        <v>-464.79</v>
+        <v>-514.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-464.79</v>
+        <v>-514.69</v>
       </c>
       <c r="Q12" s="2">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="R12" t="str">
         <v/>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>693.2</v>
+        <v>694.6</v>
       </c>
       <c r="D2" s="1">
-        <v>6.8</v>
+        <v>8.2</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0099</v>
+        <v>0.0119</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-17.9</v>
+        <v>-16.5</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0252</v>
+        <v>-0.0232</v>
       </c>
       <c r="L2" s="1">
-        <v>-17.9</v>
+        <v>-16.5</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0252</v>
+        <v>-0.0232</v>
       </c>
       <c r="N2" s="1">
-        <v>-8</v>
+        <v>-7.6</v>
       </c>
       <c r="O2" s="1">
-        <v>-21.5</v>
+        <v>-21.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-21.5</v>
+        <v>-21.1</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>10</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0099</v>
+        <v>0.0119</v>
       </c>
       <c r="U2" s="5">
-        <v>3.466</v>
+        <v>3.473</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.026</v>
+        <v>0.0239</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0365</v>
+        <v>0.0386</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.055</v>
+        <v>0.0572</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.2261</v>
+        <v>0.2286</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4282</v>
+        <v>0.4311</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>829.2</v>
+        <v>830</v>
       </c>
       <c r="D3" s="1">
-        <v>-5.2</v>
+        <v>-4.4</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0062</v>
+        <v>-0.0053</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-33.7</v>
+        <v>-32.9</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0391</v>
+        <v>-0.0381</v>
       </c>
       <c r="L3" s="1">
-        <v>-33.7</v>
+        <v>-32.9</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0391</v>
+        <v>-0.0381</v>
       </c>
       <c r="N3" s="1">
-        <v>-5.2</v>
+        <v>-5.6</v>
       </c>
       <c r="O3" s="1">
-        <v>-32.5</v>
+        <v>-32.9</v>
       </c>
       <c r="P3" s="1">
-        <v>-32.5</v>
+        <v>-32.9</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0284</v>
@@ -666,28 +666,28 @@
         <v>10</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0062</v>
+        <v>-0.0053</v>
       </c>
       <c r="U3" s="5">
-        <v>2.073</v>
+        <v>2.075</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0405</v>
+        <v>0.0395</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0254</v>
+        <v>-0.0245</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0365</v>
+        <v>0.0375</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0485</v>
+        <v>0.0495</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0736</v>
+        <v>0.0746</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>695.2</v>
+        <v>698.5</v>
       </c>
       <c r="D4" s="1">
-        <v>5.5</v>
+        <v>8.8</v>
       </c>
       <c r="E4" s="2">
-        <v>0.008</v>
+        <v>0.0128</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-41.9</v>
+        <v>-38.6</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0569</v>
+        <v>-0.0524</v>
       </c>
       <c r="L4" s="1">
-        <v>-41.9</v>
+        <v>-38.6</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0569</v>
+        <v>-0.0524</v>
       </c>
       <c r="N4" s="1">
-        <v>-19.8</v>
+        <v>-20.9</v>
       </c>
       <c r="O4" s="1">
-        <v>-43</v>
+        <v>-44.1</v>
       </c>
       <c r="P4" s="1">
-        <v>-43</v>
+        <v>-44.1</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0238</v>
+        <v>0.0239</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>10</v>
       </c>
       <c r="T4" s="2">
-        <v>0.008</v>
+        <v>0.0128</v>
       </c>
       <c r="U4" s="5">
-        <v>0.632</v>
+        <v>0.635</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0601</v>
+        <v>0.0551</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0511</v>
+        <v>-0.0466</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1259</v>
+        <v>-0.1217</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1584</v>
+        <v>-0.1544</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1425</v>
+        <v>-0.1384</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>966.8</v>
+        <v>968</v>
       </c>
       <c r="D5" s="1">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0054</v>
+        <v>0.0067</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-24.5</v>
+        <v>-23.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0247</v>
+        <v>-0.0235</v>
       </c>
       <c r="L5" s="1">
-        <v>-24.5</v>
+        <v>-23.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0247</v>
+        <v>-0.0235</v>
       </c>
       <c r="N5" s="1">
-        <v>-12.6</v>
+        <v>-11.8</v>
       </c>
       <c r="O5" s="1">
-        <v>-28.3</v>
+        <v>-27.5</v>
       </c>
       <c r="P5" s="1">
-        <v>-28.3</v>
+        <v>-27.5</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0331</v>
@@ -832,28 +832,28 @@
         <v>10</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0054</v>
+        <v>0.0067</v>
       </c>
       <c r="U5" s="5">
-        <v>4.834</v>
+        <v>4.84</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0254</v>
+        <v>0.0242</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0121</v>
+        <v>0.0134</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0349</v>
+        <v>0.0362</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0866</v>
+        <v>0.088</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2619</v>
+        <v>0.2635</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>946.2</v>
+        <v>945.7</v>
       </c>
       <c r="D6" s="1">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0013</v>
+        <v>0.0007</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-27.5</v>
+        <v>-28</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0282</v>
+        <v>-0.0288</v>
       </c>
       <c r="L6" s="1">
-        <v>-27.5</v>
+        <v>-28</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0282</v>
+        <v>-0.0288</v>
       </c>
       <c r="N6" s="1">
-        <v>-10.8</v>
+        <v>-10.5</v>
       </c>
       <c r="O6" s="1">
-        <v>-29.1</v>
+        <v>-28.8</v>
       </c>
       <c r="P6" s="1">
-        <v>-29.1</v>
+        <v>-28.8</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0324</v>
+        <v>0.0323</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>10</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0013</v>
+        <v>0.0007</v>
       </c>
       <c r="U6" s="5">
-        <v>9.462</v>
+        <v>9.457</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0291</v>
+        <v>0.0296</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0547</v>
+        <v>-0.0552</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1053</v>
+        <v>-0.1057</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0719</v>
+        <v>0.0713</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2719</v>
+        <v>0.2712</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1032</v>
+        <v>0.1031</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1063,13 +1063,13 @@
         <v>-0.0047</v>
       </c>
       <c r="N8" s="1">
-        <v>-17</v>
+        <v>-15.6</v>
       </c>
       <c r="O8" s="1">
-        <v>-9.7</v>
+        <v>-8.3</v>
       </c>
       <c r="P8" s="1">
-        <v>-9.7</v>
+        <v>-8.3</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0268</v>
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19801.6</v>
+        <v>19818.4</v>
       </c>
       <c r="D9" s="1">
-        <v>53.2</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0027</v>
+        <v>0.0035</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-576.04</v>
+        <v>-559.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0283</v>
+        <v>-0.0274</v>
       </c>
       <c r="L9" s="1">
-        <v>-576.04</v>
+        <v>-559.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0283</v>
+        <v>-0.0274</v>
       </c>
       <c r="N9" s="1">
-        <v>1.4</v>
+        <v>25.2</v>
       </c>
       <c r="O9" s="1">
-        <v>-608.24</v>
+        <v>-584.44</v>
       </c>
       <c r="P9" s="1">
-        <v>-608.24</v>
+        <v>-584.44</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6771</v>
@@ -1164,28 +1164,28 @@
         <v>10</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0027</v>
+        <v>0.0035</v>
       </c>
       <c r="U9" s="5">
-        <v>14.144</v>
+        <v>14.156</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0291</v>
+        <v>0.0282</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0093</v>
+        <v>-0.0085</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0325</v>
+        <v>-0.0317</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0503</v>
+        <v>0.0512</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1718</v>
+        <v>0.1728</v>
       </c>
     </row>
     <row r="10">
@@ -1229,13 +1229,13 @@
         <v>-0.0376</v>
       </c>
       <c r="N10" s="1">
-        <v>-11.6</v>
+        <v>-11.2</v>
       </c>
       <c r="O10" s="1">
-        <v>-24.1</v>
+        <v>-23.7</v>
       </c>
       <c r="P10" s="1">
-        <v>-24.1</v>
+        <v>-23.7</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0221</v>
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>859.2</v>
+        <v>860</v>
       </c>
       <c r="D11" s="1">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="E11" s="2">
-        <v>0.008</v>
+        <v>0.0089</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0015</v>
+        <v>-0.0006</v>
       </c>
       <c r="L11" s="1">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0015</v>
+        <v>-0.0006</v>
       </c>
       <c r="N11" s="1">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O11" s="1">
-        <v>-3.3</v>
+        <v>-3.7</v>
       </c>
       <c r="P11" s="1">
-        <v>-3.3</v>
+        <v>-3.7</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0294</v>
@@ -1330,28 +1330,28 @@
         <v>10</v>
       </c>
       <c r="T11" s="2">
-        <v>0.008</v>
+        <v>0.0089</v>
       </c>
       <c r="U11" s="5">
-        <v>2.148</v>
+        <v>2.15</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0014</v>
+        <v>0.0005</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0224</v>
+        <v>0.0233</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0468</v>
+        <v>0.0478</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2027</v>
+        <v>0.2038</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2778</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29239.8</v>
+        <v>29263.6</v>
       </c>
       <c r="D12" s="1">
-        <v>70.5</v>
+        <v>94.3</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0024</v>
+        <v>0.0032</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-751.99</v>
+        <v>-728.19</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0251</v>
+        <v>-0.0243</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-81.5</v>
+        <v>-56.3</v>
       </c>
       <c r="O12" s="1">
-        <v>-799.89</v>
+        <v>-774.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-799.89</v>
+        <v>-774.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9999</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>694.6</v>
+        <v>689.2</v>
       </c>
       <c r="D2" s="1">
-        <v>8.2</v>
+        <v>2.8</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0119</v>
+        <v>0.0041</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-16.5</v>
+        <v>-21.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0232</v>
+        <v>-0.0308</v>
       </c>
       <c r="L2" s="1">
-        <v>-16.5</v>
+        <v>-21.9</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0232</v>
+        <v>-0.0308</v>
       </c>
       <c r="N2" s="1">
-        <v>-7.6</v>
+        <v>-8.6</v>
       </c>
       <c r="O2" s="1">
-        <v>-21.1</v>
+        <v>-22.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-21.1</v>
+        <v>-22.1</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0237</v>
+        <v>0.0236</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>10</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0119</v>
+        <v>0.0041</v>
       </c>
       <c r="U2" s="5">
-        <v>3.473</v>
+        <v>3.446</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0239</v>
+        <v>0.0319</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0386</v>
+        <v>0.0305</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0572</v>
+        <v>0.049</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.2286</v>
+        <v>0.2191</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4311</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="3">
@@ -648,13 +648,13 @@
         <v>-0.0381</v>
       </c>
       <c r="N3" s="1">
-        <v>-5.6</v>
+        <v>-6</v>
       </c>
       <c r="O3" s="1">
-        <v>-32.9</v>
+        <v>-33.3</v>
       </c>
       <c r="P3" s="1">
-        <v>-32.9</v>
+        <v>-33.3</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0284</v>
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>698.5</v>
+        <v>696.3</v>
       </c>
       <c r="D4" s="1">
-        <v>8.8</v>
+        <v>6.6</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0128</v>
+        <v>0.0096</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-38.6</v>
+        <v>-40.8</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0524</v>
+        <v>-0.0554</v>
       </c>
       <c r="L4" s="1">
-        <v>-38.6</v>
+        <v>-40.8</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0524</v>
+        <v>-0.0554</v>
       </c>
       <c r="N4" s="1">
-        <v>-20.9</v>
+        <v>-18.7</v>
       </c>
       <c r="O4" s="1">
-        <v>-44.1</v>
+        <v>-41.9</v>
       </c>
       <c r="P4" s="1">
-        <v>-44.1</v>
+        <v>-41.9</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0239</v>
+        <v>0.0238</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>10</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0128</v>
+        <v>0.0096</v>
       </c>
       <c r="U4" s="5">
-        <v>0.635</v>
+        <v>0.633</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0551</v>
+        <v>0.0585</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0466</v>
+        <v>-0.0496</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1217</v>
+        <v>-0.1245</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1544</v>
+        <v>-0.1571</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1384</v>
+        <v>-0.1412</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>968</v>
+        <v>965.2</v>
       </c>
       <c r="D5" s="1">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0067</v>
+        <v>0.0037</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-23.3</v>
+        <v>-26.1</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0235</v>
+        <v>-0.0263</v>
       </c>
       <c r="L5" s="1">
-        <v>-23.3</v>
+        <v>-26.1</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0235</v>
+        <v>-0.0263</v>
       </c>
       <c r="N5" s="1">
-        <v>-11.8</v>
+        <v>-12.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-27.5</v>
+        <v>-28.1</v>
       </c>
       <c r="P5" s="1">
-        <v>-27.5</v>
+        <v>-28.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0331</v>
+        <v>0.033</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>10</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0067</v>
+        <v>0.0037</v>
       </c>
       <c r="U5" s="5">
-        <v>4.84</v>
+        <v>4.826</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0242</v>
+        <v>0.0271</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0134</v>
+        <v>0.0105</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0362</v>
+        <v>0.0332</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.088</v>
+        <v>0.0848</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2635</v>
+        <v>0.2598</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>945.7</v>
+        <v>944.7</v>
       </c>
       <c r="D6" s="1">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0288</v>
+        <v>-0.0298</v>
       </c>
       <c r="L6" s="1">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0288</v>
+        <v>-0.0298</v>
       </c>
       <c r="N6" s="1">
-        <v>-10.5</v>
+        <v>-9.9</v>
       </c>
       <c r="O6" s="1">
-        <v>-28.8</v>
+        <v>-28.2</v>
       </c>
       <c r="P6" s="1">
-        <v>-28.8</v>
+        <v>-28.2</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0323</v>
@@ -915,28 +915,28 @@
         <v>10</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="U6" s="5">
-        <v>9.457</v>
+        <v>9.447</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0296</v>
+        <v>0.0307</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0552</v>
+        <v>-0.0562</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1057</v>
+        <v>-0.1067</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0713</v>
+        <v>0.0702</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2712</v>
+        <v>0.2699</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1031</v>
+        <v>0.1034</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>783</v>
+        <v>778.6</v>
       </c>
       <c r="D8" s="1">
-        <v>13.8</v>
+        <v>9.4</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0179</v>
+        <v>0.0122</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-3.7</v>
+        <v>-8.1</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0047</v>
+        <v>-0.0103</v>
       </c>
       <c r="L8" s="1">
-        <v>-3.7</v>
+        <v>-8.1</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0047</v>
+        <v>-0.0103</v>
       </c>
       <c r="N8" s="1">
-        <v>-15.6</v>
+        <v>-18</v>
       </c>
       <c r="O8" s="1">
-        <v>-8.3</v>
+        <v>-10.7</v>
       </c>
       <c r="P8" s="1">
-        <v>-8.3</v>
+        <v>-10.7</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0268</v>
+        <v>0.0267</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>10</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0179</v>
+        <v>0.0122</v>
       </c>
       <c r="U8" s="5">
-        <v>3.915</v>
+        <v>3.893</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0049</v>
+        <v>0.0105</v>
       </c>
       <c r="X8" s="2">
-        <v>0.0635</v>
+        <v>0.0576</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.199</v>
+        <v>0.1923</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3482</v>
+        <v>0.3406</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9248</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19818.4</v>
+        <v>19770.8</v>
       </c>
       <c r="D9" s="1">
-        <v>70</v>
+        <v>22.4</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0035</v>
+        <v>0.0011</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-559.24</v>
+        <v>-606.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0274</v>
+        <v>-0.0298</v>
       </c>
       <c r="L9" s="1">
-        <v>-559.24</v>
+        <v>-606.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0274</v>
+        <v>-0.0298</v>
       </c>
       <c r="N9" s="1">
-        <v>25.2</v>
+        <v>-15.4</v>
       </c>
       <c r="O9" s="1">
-        <v>-584.44</v>
+        <v>-625.04</v>
       </c>
       <c r="P9" s="1">
-        <v>-584.44</v>
+        <v>-625.04</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6771</v>
+        <v>0.6769</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>10</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0035</v>
+        <v>0.0011</v>
       </c>
       <c r="U9" s="5">
-        <v>14.156</v>
+        <v>14.122</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0282</v>
+        <v>0.0307</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0085</v>
+        <v>-0.0109</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0317</v>
+        <v>-0.034</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0512</v>
+        <v>0.0487</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1728</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="10">
@@ -1279,46 +1279,46 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>860</v>
+        <v>858.4</v>
       </c>
       <c r="D11" s="1">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.007</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" s="2">
+        <v/>
+      </c>
+      <c r="H11" s="1">
+        <v/>
+      </c>
+      <c r="I11" s="2">
+        <v/>
+      </c>
+      <c r="J11" s="1">
+        <v>-2.1</v>
+      </c>
+      <c r="K11" s="2">
+        <v>-0.0024</v>
+      </c>
+      <c r="L11" s="1">
+        <v>-2.1</v>
+      </c>
+      <c r="M11" s="2">
+        <v>-0.0024</v>
+      </c>
+      <c r="N11" s="1">
         <v>7.6</v>
       </c>
-      <c r="E11" s="2">
-        <v>0.0089</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" s="2">
-        <v/>
-      </c>
-      <c r="H11" s="1">
-        <v/>
-      </c>
-      <c r="I11" s="2">
-        <v/>
-      </c>
-      <c r="J11" s="1">
+      <c r="O11" s="1">
         <v>-0.5</v>
       </c>
-      <c r="K11" s="2">
-        <v>-0.0006</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="P11" s="1">
         <v>-0.5</v>
-      </c>
-      <c r="M11" s="2">
-        <v>-0.0006</v>
-      </c>
-      <c r="N11" s="1">
-        <v>4.4</v>
-      </c>
-      <c r="O11" s="1">
-        <v>-3.7</v>
-      </c>
-      <c r="P11" s="1">
-        <v>-3.7</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0294</v>
@@ -1330,28 +1330,28 @@
         <v>10</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0089</v>
+        <v>0.007</v>
       </c>
       <c r="U11" s="5">
-        <v>2.15</v>
+        <v>2.146</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0005</v>
+        <v>0.0023</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0233</v>
+        <v>0.0214</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0478</v>
+        <v>0.0458</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2038</v>
+        <v>0.2016</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.279</v>
+        <v>0.2766</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29263.6</v>
+        <v>29198.6</v>
       </c>
       <c r="D12" s="1">
-        <v>94.3</v>
+        <v>29.3</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0032</v>
+        <v>0.001</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-728.19</v>
+        <v>-793.19</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0243</v>
+        <v>-0.0264</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,16 +1395,16 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-56.3</v>
+        <v>-95.3</v>
       </c>
       <c r="O12" s="1">
-        <v>-774.69</v>
+        <v>-813.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-774.69</v>
+        <v>-813.69</v>
       </c>
       <c r="Q12" s="2">
-        <v>0.9999</v>
+        <v>0.9997</v>
       </c>
       <c r="R12" t="str">
         <v/>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>689.2</v>
+        <v>695</v>
       </c>
       <c r="D2" s="1">
-        <v>2.8</v>
+        <v>8.6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0041</v>
+        <v>0.0125</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-21.9</v>
+        <v>-16.1</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0308</v>
+        <v>-0.0226</v>
       </c>
       <c r="L2" s="1">
-        <v>-21.9</v>
+        <v>-16.1</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0308</v>
+        <v>-0.0226</v>
       </c>
       <c r="N2" s="1">
-        <v>-8.6</v>
+        <v>-2.6</v>
       </c>
       <c r="O2" s="1">
-        <v>-22.1</v>
+        <v>-16.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-22.1</v>
+        <v>-16.1</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0236</v>
+        <v>0.0238</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>10</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0041</v>
+        <v>0.0125</v>
       </c>
       <c r="U2" s="5">
-        <v>3.446</v>
+        <v>3.475</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0319</v>
+        <v>0.0233</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0305</v>
+        <v>0.0392</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.049</v>
+        <v>0.0578</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.2191</v>
+        <v>0.2293</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.42</v>
+        <v>0.4319</v>
       </c>
     </row>
     <row r="3">
@@ -615,46 +615,46 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>830</v>
+        <v>831.2</v>
       </c>
       <c r="D3" s="1">
+        <v>-3.2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>-0.0038</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="2">
+        <v/>
+      </c>
+      <c r="H3" s="1">
+        <v/>
+      </c>
+      <c r="I3" s="2">
+        <v/>
+      </c>
+      <c r="J3" s="1">
+        <v>-31.7</v>
+      </c>
+      <c r="K3" s="2">
+        <v>-0.0367</v>
+      </c>
+      <c r="L3" s="1">
+        <v>-31.7</v>
+      </c>
+      <c r="M3" s="2">
+        <v>-0.0367</v>
+      </c>
+      <c r="N3" s="1">
         <v>-4.4</v>
       </c>
-      <c r="E3" s="2">
-        <v>-0.0053</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" s="2">
-        <v/>
-      </c>
-      <c r="H3" s="1">
-        <v/>
-      </c>
-      <c r="I3" s="2">
-        <v/>
-      </c>
-      <c r="J3" s="1">
-        <v>-32.9</v>
-      </c>
-      <c r="K3" s="2">
-        <v>-0.0381</v>
-      </c>
-      <c r="L3" s="1">
-        <v>-32.9</v>
-      </c>
-      <c r="M3" s="2">
-        <v>-0.0381</v>
-      </c>
-      <c r="N3" s="1">
-        <v>-6</v>
-      </c>
       <c r="O3" s="1">
-        <v>-33.3</v>
+        <v>-31.7</v>
       </c>
       <c r="P3" s="1">
-        <v>-33.3</v>
+        <v>-31.7</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0284</v>
@@ -666,28 +666,28 @@
         <v>10</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="U3" s="5">
-        <v>2.075</v>
+        <v>2.078</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0395</v>
+        <v>0.038</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0245</v>
+        <v>-0.0231</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0375</v>
+        <v>0.039</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0495</v>
+        <v>0.0511</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0746</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>696.3</v>
+        <v>699.6</v>
       </c>
       <c r="D4" s="1">
-        <v>6.6</v>
+        <v>9.9</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0096</v>
+        <v>0.0144</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-40.8</v>
+        <v>-37.5</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0554</v>
+        <v>-0.0509</v>
       </c>
       <c r="L4" s="1">
-        <v>-40.8</v>
+        <v>-37.5</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0554</v>
+        <v>-0.0509</v>
       </c>
       <c r="N4" s="1">
-        <v>-18.7</v>
+        <v>-14.3</v>
       </c>
       <c r="O4" s="1">
-        <v>-41.9</v>
+        <v>-37.5</v>
       </c>
       <c r="P4" s="1">
-        <v>-41.9</v>
+        <v>-37.5</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0238</v>
+        <v>0.0239</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>10</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0096</v>
+        <v>0.0144</v>
       </c>
       <c r="U4" s="5">
-        <v>0.633</v>
+        <v>0.636</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0585</v>
+        <v>0.0535</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0496</v>
+        <v>-0.0451</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1245</v>
+        <v>-0.1204</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1571</v>
+        <v>-0.1531</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1412</v>
+        <v>-0.1371</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>965.2</v>
+        <v>967</v>
       </c>
       <c r="D5" s="1">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0037</v>
+        <v>0.0056</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-26.1</v>
+        <v>-24.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0263</v>
+        <v>-0.0245</v>
       </c>
       <c r="L5" s="1">
-        <v>-26.1</v>
+        <v>-24.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0263</v>
+        <v>-0.0245</v>
       </c>
       <c r="N5" s="1">
-        <v>-12.4</v>
+        <v>-8.6</v>
       </c>
       <c r="O5" s="1">
-        <v>-28.1</v>
+        <v>-24.3</v>
       </c>
       <c r="P5" s="1">
-        <v>-28.1</v>
+        <v>-24.3</v>
       </c>
       <c r="Q5" s="2">
         <v>0.033</v>
@@ -832,28 +832,28 @@
         <v>10</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0037</v>
+        <v>0.0056</v>
       </c>
       <c r="U5" s="5">
-        <v>4.826</v>
+        <v>4.835</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0271</v>
+        <v>0.0252</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0105</v>
+        <v>0.0124</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0332</v>
+        <v>0.0351</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0848</v>
+        <v>0.0869</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2598</v>
+        <v>0.2621</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>944.7</v>
+        <v>944.8</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-29</v>
+        <v>-28.9</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0298</v>
+        <v>-0.0297</v>
       </c>
       <c r="L6" s="1">
-        <v>-29</v>
+        <v>-28.9</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0298</v>
+        <v>-0.0297</v>
       </c>
       <c r="N6" s="1">
-        <v>-9.9</v>
+        <v>-10.6</v>
       </c>
       <c r="O6" s="1">
-        <v>-28.2</v>
+        <v>-28.9</v>
       </c>
       <c r="P6" s="1">
-        <v>-28.2</v>
+        <v>-28.9</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0323</v>
@@ -915,28 +915,28 @@
         <v>10</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="U6" s="5">
-        <v>9.447</v>
+        <v>9.448</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0307</v>
+        <v>0.0306</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0562</v>
+        <v>-0.0561</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1067</v>
+        <v>-0.1066</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0702</v>
+        <v>0.0703</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2699</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1034</v>
+        <v>0.1032</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>778.6</v>
+        <v>782.6</v>
       </c>
       <c r="D8" s="1">
-        <v>9.4</v>
+        <v>13.4</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0122</v>
+        <v>0.0174</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-8.1</v>
+        <v>-4.1</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0103</v>
+        <v>-0.0052</v>
       </c>
       <c r="L8" s="1">
-        <v>-8.1</v>
+        <v>-4.1</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0103</v>
+        <v>-0.0052</v>
       </c>
       <c r="N8" s="1">
-        <v>-18</v>
+        <v>-11.4</v>
       </c>
       <c r="O8" s="1">
-        <v>-10.7</v>
+        <v>-4.1</v>
       </c>
       <c r="P8" s="1">
-        <v>-10.7</v>
+        <v>-4.1</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0267</v>
@@ -1081,28 +1081,28 @@
         <v>10</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0122</v>
+        <v>0.0174</v>
       </c>
       <c r="U8" s="5">
-        <v>3.893</v>
+        <v>3.913</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0105</v>
+        <v>0.0054</v>
       </c>
       <c r="X8" s="2">
-        <v>0.0576</v>
+        <v>0.063</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1923</v>
+        <v>0.1984</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3406</v>
+        <v>0.3475</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.914</v>
+        <v>0.9238</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19770.8</v>
+        <v>19812.8</v>
       </c>
       <c r="D9" s="1">
-        <v>22.4</v>
+        <v>64.4</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0011</v>
+        <v>0.0033</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-606.84</v>
+        <v>-564.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0298</v>
+        <v>-0.0277</v>
       </c>
       <c r="L9" s="1">
-        <v>-606.84</v>
+        <v>-564.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0298</v>
+        <v>-0.0277</v>
       </c>
       <c r="N9" s="1">
-        <v>-15.4</v>
+        <v>44.8</v>
       </c>
       <c r="O9" s="1">
-        <v>-625.04</v>
+        <v>-564.84</v>
       </c>
       <c r="P9" s="1">
-        <v>-625.04</v>
+        <v>-564.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6769</v>
+        <v>0.6771</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>10</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0011</v>
+        <v>0.0033</v>
       </c>
       <c r="U9" s="5">
-        <v>14.122</v>
+        <v>14.152</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0307</v>
+        <v>0.0285</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0109</v>
+        <v>-0.0088</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.034</v>
+        <v>-0.032</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0487</v>
+        <v>0.0509</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.17</v>
+        <v>0.1725</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>646.8</v>
+        <v>643.6</v>
       </c>
       <c r="D10" s="1">
-        <v>-16.8</v>
+        <v>-20</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0253</v>
+        <v>-0.0301</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-25.3</v>
+        <v>-28.5</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0376</v>
+        <v>-0.0424</v>
       </c>
       <c r="L10" s="1">
-        <v>-25.3</v>
+        <v>-28.5</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0376</v>
+        <v>-0.0424</v>
       </c>
       <c r="N10" s="1">
-        <v>-11.2</v>
+        <v>-16</v>
       </c>
       <c r="O10" s="1">
-        <v>-23.7</v>
+        <v>-28.5</v>
       </c>
       <c r="P10" s="1">
-        <v>-23.7</v>
+        <v>-28.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0221</v>
+        <v>0.022</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>10</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0253</v>
+        <v>-0.0301</v>
       </c>
       <c r="U10" s="5">
-        <v>1.617</v>
+        <v>1.609</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.039</v>
+        <v>0.0441</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.008</v>
+        <v>-0.0129</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2742</v>
+        <v>0.2679</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3566</v>
+        <v>0.3499</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2306</v>
+        <v>0.2245</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>858.4</v>
+        <v>859.2</v>
       </c>
       <c r="D11" s="1">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="E11" s="2">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-2.1</v>
+        <v>-1.3</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0024</v>
+        <v>-0.0015</v>
       </c>
       <c r="L11" s="1">
-        <v>-2.1</v>
+        <v>-1.3</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0024</v>
+        <v>-0.0015</v>
       </c>
       <c r="N11" s="1">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="O11" s="1">
-        <v>-0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0294</v>
@@ -1330,28 +1330,28 @@
         <v>10</v>
       </c>
       <c r="T11" s="2">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="U11" s="5">
-        <v>2.146</v>
+        <v>2.148</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0023</v>
+        <v>0.0014</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0214</v>
+        <v>0.0224</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0458</v>
+        <v>0.0468</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2016</v>
+        <v>0.2027</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2766</v>
+        <v>0.2778</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29198.6</v>
+        <v>29254.4</v>
       </c>
       <c r="D12" s="1">
-        <v>29.3</v>
+        <v>85.1</v>
       </c>
       <c r="E12" s="2">
-        <v>0.001</v>
+        <v>0.0029</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-793.19</v>
+        <v>-737.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0264</v>
+        <v>-0.0246</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-95.3</v>
+        <v>-19</v>
       </c>
       <c r="O12" s="1">
-        <v>-813.69</v>
+        <v>-737.39</v>
       </c>
       <c r="P12" s="1">
-        <v>-813.69</v>
+        <v>-737.39</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>700.2</v>
+        <v>707.8</v>
       </c>
       <c r="D2" s="1">
-        <v>1.2</v>
+        <v>8.8</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-10.9</v>
+        <v>-3.3</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0153</v>
+        <v>-0.0046</v>
       </c>
       <c r="L2" s="1">
-        <v>-10.9</v>
+        <v>-3.3</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0153</v>
+        <v>-0.0046</v>
       </c>
       <c r="N2" s="1">
-        <v>4.6</v>
+        <v>12.8</v>
       </c>
       <c r="O2" s="1">
-        <v>-11.1</v>
+        <v>-3.3</v>
       </c>
       <c r="P2" s="1">
-        <v>-11.1</v>
+        <v>-3.3</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0239</v>
+        <v>0.0241</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>11</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="U2" s="5">
-        <v>3.501</v>
+        <v>3.539</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0157</v>
+        <v>0.0048</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0526</v>
+        <v>0.064</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0539</v>
+        <v>0.0653</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.2244</v>
+        <v>0.2377</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4756</v>
+        <v>0.4916</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>838</v>
+        <v>822.4</v>
       </c>
       <c r="D3" s="1">
-        <v>4.4</v>
+        <v>-11.2</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0053</v>
+        <v>-0.0134</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-24.9</v>
+        <v>-40.5</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0289</v>
+        <v>-0.0469</v>
       </c>
       <c r="L3" s="1">
-        <v>-24.9</v>
+        <v>-40.5</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0289</v>
+        <v>-0.0469</v>
       </c>
       <c r="N3" s="1">
-        <v>6.8</v>
+        <v>-8.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-24.1</v>
+        <v>-40.5</v>
       </c>
       <c r="P3" s="1">
-        <v>-24.1</v>
+        <v>-40.5</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0286</v>
+        <v>0.0281</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>11</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0053</v>
+        <v>-0.0134</v>
       </c>
       <c r="U3" s="5">
-        <v>2.095</v>
+        <v>2.056</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0296</v>
+        <v>0.0491</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0141</v>
+        <v>-0.0325</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.047</v>
+        <v>0.0275</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0444</v>
+        <v>0.0249</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0906</v>
+        <v>0.0703</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>695.2</v>
+        <v>699.6</v>
       </c>
       <c r="D4" s="1">
-        <v>-6.6</v>
+        <v>-2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0094</v>
+        <v>-0.0031</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-41.9</v>
+        <v>-37.5</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0569</v>
+        <v>-0.0509</v>
       </c>
       <c r="L4" s="1">
-        <v>-41.9</v>
+        <v>-37.5</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0569</v>
+        <v>-0.0509</v>
       </c>
       <c r="N4" s="1">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1">
-        <v>-40.8</v>
+        <v>-37.5</v>
       </c>
       <c r="P4" s="1">
-        <v>-40.8</v>
+        <v>-37.5</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0237</v>
+        <v>0.0239</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>11</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0094</v>
+        <v>-0.0031</v>
       </c>
       <c r="U4" s="5">
-        <v>0.632</v>
+        <v>0.636</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0601</v>
+        <v>0.0535</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0202</v>
+        <v>-0.014</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1023</v>
+        <v>-0.0966</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1749</v>
+        <v>-0.1697</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1234</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>974.8</v>
+        <v>987.4</v>
       </c>
       <c r="D5" s="1">
-        <v>2.4</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0025</v>
+        <v>0.0154</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-16.5</v>
+        <v>-3.9</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0166</v>
+        <v>-0.0039</v>
       </c>
       <c r="L5" s="1">
-        <v>-16.5</v>
+        <v>-3.9</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0166</v>
+        <v>-0.0039</v>
       </c>
       <c r="N5" s="1">
-        <v>7.8</v>
+        <v>20.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-16.9</v>
+        <v>-3.9</v>
       </c>
       <c r="P5" s="1">
-        <v>-16.9</v>
+        <v>-3.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0333</v>
+        <v>0.0337</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>11</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0025</v>
+        <v>0.0154</v>
       </c>
       <c r="U5" s="5">
-        <v>4.874</v>
+        <v>4.937</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.017</v>
+        <v>0.0041</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0192</v>
+        <v>0.0324</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0335</v>
+        <v>0.0469</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0973</v>
+        <v>0.1115</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2823</v>
+        <v>0.2988</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>952</v>
+        <v>951.2</v>
       </c>
       <c r="D6" s="1">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0062</v>
+        <v>0.0054</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0223</v>
+        <v>-0.0231</v>
       </c>
       <c r="L6" s="1">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0223</v>
+        <v>-0.0231</v>
       </c>
       <c r="N6" s="1">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="O6" s="1">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="P6" s="1">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0325</v>
+        <v>0.0324</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>11</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0062</v>
+        <v>0.0054</v>
       </c>
       <c r="U6" s="5">
-        <v>9.52</v>
+        <v>9.512</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0228</v>
+        <v>0.0237</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0311</v>
+        <v>-0.0319</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1306</v>
+        <v>-0.1313</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0749</v>
+        <v>0.074</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2772</v>
+        <v>0.2761</v>
       </c>
     </row>
     <row r="7">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>785</v>
+        <v>806.8</v>
       </c>
       <c r="D8" s="1">
-        <v>-4.2</v>
+        <v>17.6</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0053</v>
+        <v>0.0223</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-1.7</v>
+        <v>20.1</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0022</v>
+        <v>0.0255</v>
       </c>
       <c r="L8" s="1">
-        <v>-1.7</v>
+        <v>20.1</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0022</v>
+        <v>0.0255</v>
       </c>
       <c r="N8" s="1">
-        <v>2.8</v>
+        <v>24.2</v>
       </c>
       <c r="O8" s="1">
-        <v>-1.3</v>
+        <v>20.1</v>
       </c>
       <c r="P8" s="1">
-        <v>-1.3</v>
+        <v>20.1</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0268</v>
+        <v>0.0275</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>11</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0053</v>
+        <v>0.0223</v>
       </c>
       <c r="U8" s="5">
-        <v>3.925</v>
+        <v>4.034</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0023</v>
+        <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0683</v>
+        <v>0.098</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1912</v>
+        <v>0.2243</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3497</v>
+        <v>0.3872</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9684</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19824</v>
+        <v>19821.2</v>
       </c>
       <c r="D9" s="1">
-        <v>37.8</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-553.64</v>
+        <v>-556.44</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0272</v>
+        <v>-0.0273</v>
       </c>
       <c r="L9" s="1">
-        <v>-553.64</v>
+        <v>-556.44</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0272</v>
+        <v>-0.0273</v>
       </c>
       <c r="N9" s="1">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="O9" s="1">
-        <v>-570.44</v>
+        <v>-556.44</v>
       </c>
       <c r="P9" s="1">
-        <v>-570.44</v>
+        <v>-556.44</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6766</v>
+        <v>0.6761</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>11</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="U9" s="5">
-        <v>14.16</v>
+        <v>14.158</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0279</v>
+        <v>0.028</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.006</v>
+        <v>-0.0061</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0393</v>
+        <v>-0.0394</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0524</v>
+        <v>0.0523</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1812</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>643.6</v>
+        <v>632</v>
       </c>
       <c r="D10" s="1">
-        <v>-4.8</v>
+        <v>-16.4</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0074</v>
+        <v>-0.0253</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-28.5</v>
+        <v>-40.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0424</v>
+        <v>-0.0597</v>
       </c>
       <c r="L10" s="1">
-        <v>-28.5</v>
+        <v>-40.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0424</v>
+        <v>-0.0597</v>
       </c>
       <c r="N10" s="1">
-        <v>-0.8</v>
+        <v>-11.6</v>
       </c>
       <c r="O10" s="1">
-        <v>-30.1</v>
+        <v>-40.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-30.1</v>
+        <v>-40.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.022</v>
+        <v>0.0216</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>11</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0074</v>
+        <v>-0.0253</v>
       </c>
       <c r="U10" s="5">
-        <v>1.609</v>
+        <v>1.58</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0441</v>
+        <v>0.0633</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.0319</v>
+        <v>-0.0494</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2264</v>
+        <v>0.2043</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3265</v>
+        <v>0.3026</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2483</v>
+        <v>0.2258</v>
       </c>
     </row>
     <row r="11">
@@ -1312,13 +1312,13 @@
         <v>0.0055</v>
       </c>
       <c r="N11" s="1">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O11" s="1">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="P11" s="1">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0295</v>
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29296.6</v>
+        <v>29312.2</v>
       </c>
       <c r="D12" s="1">
-        <v>38.2</v>
+        <v>53.8</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-695.19</v>
+        <v>-679.59</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0232</v>
+        <v>-0.0227</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>51.4</v>
+        <v>57.8</v>
       </c>
       <c r="O12" s="1">
-        <v>-711.49</v>
+        <v>-679.59</v>
       </c>
       <c r="P12" s="1">
-        <v>-711.49</v>
+        <v>-679.59</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9999</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>685.2</v>
+        <v>696.4</v>
       </c>
       <c r="D2" s="1">
-        <v>-2.2</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0032</v>
+        <v>0.0029</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,58 +553,58 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-25.9</v>
+        <v>-14.7</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0364</v>
+        <v>-0.0207</v>
       </c>
       <c r="L2" s="1">
-        <v>-25.9</v>
+        <v>-14.7</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0364</v>
+        <v>-0.0207</v>
       </c>
       <c r="N2" s="1">
-        <v>-10.6</v>
+        <v>-2.6</v>
       </c>
       <c r="O2" s="1">
-        <v>-25.9</v>
+        <v>-14.7</v>
       </c>
       <c r="P2" s="1">
-        <v>-25.9</v>
+        <v>-14.7</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0235</v>
+        <v>0.0238</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
       </c>
       <c r="S2" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0032</v>
+        <v>0.0029</v>
       </c>
       <c r="U2" s="5">
-        <v>3.426</v>
+        <v>3.482</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0379</v>
+        <v>0.0213</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0261</v>
+        <v>0.0561</v>
       </c>
       <c r="Y2" s="2">
-        <v>-0.0015</v>
+        <v>0.0148</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1814</v>
+        <v>0.1882</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4399</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>828.8</v>
+        <v>836.4</v>
       </c>
       <c r="D3" s="1">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0019</v>
+        <v>0.0034</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,58 +636,58 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-34.1</v>
+        <v>-26.5</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0395</v>
+        <v>-0.0307</v>
       </c>
       <c r="L3" s="1">
-        <v>-34.1</v>
+        <v>-26.5</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0395</v>
+        <v>-0.0307</v>
       </c>
       <c r="N3" s="1">
-        <v>-4</v>
+        <v>4.4</v>
       </c>
       <c r="O3" s="1">
-        <v>-34.1</v>
+        <v>-24.9</v>
       </c>
       <c r="P3" s="1">
-        <v>-34.1</v>
+        <v>-24.9</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0284</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
       </c>
       <c r="S3" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0019</v>
+        <v>0.0034</v>
       </c>
       <c r="U3" s="5">
-        <v>2.072</v>
+        <v>2.091</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.041</v>
+        <v>0.0316</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0371</v>
+        <v>-0.0315</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0273</v>
+        <v>0.0367</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0227</v>
+        <v>0.0331</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0742</v>
+        <v>0.0879</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>704</v>
+        <v>709.5</v>
       </c>
       <c r="D4" s="1">
-        <v>1.1</v>
+        <v>8.8</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0016</v>
+        <v>0.0126</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,58 +719,58 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-33.1</v>
+        <v>-27.6</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0449</v>
+        <v>-0.0374</v>
       </c>
       <c r="L4" s="1">
-        <v>-33.1</v>
+        <v>-27.6</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0449</v>
+        <v>-0.0374</v>
       </c>
       <c r="N4" s="1">
-        <v>4.4</v>
+        <v>8.8</v>
       </c>
       <c r="O4" s="1">
-        <v>-33.1</v>
+        <v>-26.5</v>
       </c>
       <c r="P4" s="1">
-        <v>-33.1</v>
+        <v>-26.5</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0241</v>
+        <v>0.0242</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
       </c>
       <c r="S4" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0016</v>
+        <v>0.0126</v>
       </c>
       <c r="U4" s="5">
-        <v>0.64</v>
+        <v>0.645</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0469</v>
+        <v>0.0388</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0169</v>
+        <v>0.0094</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0657</v>
+        <v>-0.0584</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1688</v>
+        <v>-0.1645</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1036</v>
+        <v>-0.0941</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>981</v>
+        <v>990.8</v>
       </c>
       <c r="D5" s="1">
-        <v>-5.4</v>
+        <v>4.4</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0055</v>
+        <v>0.0045</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,58 +802,58 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-10.3</v>
+        <v>-0.5</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0104</v>
+        <v>-0.0005</v>
       </c>
       <c r="L5" s="1">
-        <v>-10.3</v>
+        <v>-0.5</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0104</v>
+        <v>-0.0005</v>
       </c>
       <c r="N5" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O5" s="1">
-        <v>-10.3</v>
+        <v>0.1</v>
       </c>
       <c r="P5" s="1">
-        <v>-10.3</v>
+        <v>0.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0336</v>
+        <v>0.0338</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
       </c>
       <c r="S5" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0055</v>
+        <v>0.0045</v>
       </c>
       <c r="U5" s="5">
-        <v>4.905</v>
+        <v>4.954</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0106</v>
+        <v>0.0006</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0258</v>
+        <v>0.0386</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0381</v>
+        <v>0.0485</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0888</v>
+        <v>0.0966</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3041</v>
+        <v>0.3185</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>920.9</v>
+        <v>936.2</v>
       </c>
       <c r="D6" s="1">
-        <v>-13.6</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0146</v>
+        <v>0.0252</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,58 +885,58 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-52.8</v>
+        <v>-37.5</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0542</v>
+        <v>-0.0385</v>
       </c>
       <c r="L6" s="1">
-        <v>-52.8</v>
+        <v>-37.5</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0542</v>
+        <v>-0.0385</v>
       </c>
       <c r="N6" s="1">
-        <v>-23.9</v>
+        <v>-9.9</v>
       </c>
       <c r="O6" s="1">
-        <v>-52.1</v>
+        <v>-37.5</v>
       </c>
       <c r="P6" s="1">
-        <v>-52.1</v>
+        <v>-37.5</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0315</v>
+        <v>0.0319</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
       </c>
       <c r="S6" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0146</v>
+        <v>0.0252</v>
       </c>
       <c r="U6" s="5">
-        <v>9.209</v>
+        <v>9.362</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0573</v>
+        <v>0.0401</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0695</v>
+        <v>-0.0381</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1576</v>
+        <v>-0.1437</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0221</v>
+        <v>0.0326</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2502</v>
+        <v>0.2694</v>
       </c>
     </row>
     <row r="7">
@@ -947,7 +947,7 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3026.7</v>
+        <v>3032.1</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -968,40 +968,40 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0026</v>
+        <v>0.0044</v>
       </c>
       <c r="L7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0026</v>
+        <v>0.0044</v>
       </c>
       <c r="N7" s="1">
-        <v>8.1</v>
+        <v>10.8</v>
       </c>
       <c r="O7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="P7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1037</v>
+        <v>0.1034</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
       </c>
       <c r="S7" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T7" s="2">
         <v>0</v>
       </c>
       <c r="U7" s="5">
-        <v>1.121</v>
+        <v>1.123</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0036</v>
+        <v>0.0054</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0117</v>
+        <v>0.0135</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0145</v>
+        <v>0.0163</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0206</v>
+        <v>0.0224</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>807.8</v>
+        <v>831</v>
       </c>
       <c r="D8" s="1">
-        <v>-3.4</v>
+        <v>3.4</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0042</v>
+        <v>0.0041</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,40 +1051,40 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>21.1</v>
+        <v>44.3</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0268</v>
+        <v>0.0563</v>
       </c>
       <c r="L8" s="1">
-        <v>21.1</v>
+        <v>44.3</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0268</v>
+        <v>0.0563</v>
       </c>
       <c r="N8" s="1">
-        <v>25.2</v>
+        <v>43.2</v>
       </c>
       <c r="O8" s="1">
-        <v>21.9</v>
+        <v>45.7</v>
       </c>
       <c r="P8" s="1">
-        <v>21.9</v>
+        <v>45.7</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0277</v>
+        <v>0.0283</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
       </c>
       <c r="S8" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0042</v>
+        <v>0.0041</v>
       </c>
       <c r="U8" s="5">
-        <v>4.039</v>
+        <v>4.155</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1059</v>
+        <v>0.1535</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2236</v>
+        <v>0.2588</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.341</v>
+        <v>0.369</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0534</v>
+        <v>1.121</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19569.2</v>
+        <v>19790.4</v>
       </c>
       <c r="D9" s="1">
-        <v>-42</v>
+        <v>15.4</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0021</v>
+        <v>0.0008</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,58 +1134,58 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-808.44</v>
+        <v>-587.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0397</v>
+        <v>-0.0288</v>
       </c>
       <c r="L9" s="1">
-        <v>-808.44</v>
+        <v>-587.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0397</v>
+        <v>-0.0288</v>
       </c>
       <c r="N9" s="1">
-        <v>-233.8</v>
+        <v>15.4</v>
       </c>
       <c r="O9" s="1">
-        <v>-808.44</v>
+        <v>-576.04</v>
       </c>
       <c r="P9" s="1">
-        <v>-808.44</v>
+        <v>-576.04</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6702</v>
+        <v>0.675</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
       </c>
       <c r="S9" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0021</v>
+        <v>0.0008</v>
       </c>
       <c r="U9" s="5">
-        <v>13.978</v>
+        <v>14.136</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0413</v>
+        <v>0.0296</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0225</v>
+        <v>-0.0036</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0424</v>
+        <v>-0.0315</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0511</v>
+        <v>0.0558</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1707</v>
+        <v>0.1837</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D10" s="1">
-        <v>8.8</v>
+        <v>-4</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0139</v>
+        <v>-0.0063</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,58 +1217,58 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-32.1</v>
+        <v>-36.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0478</v>
+        <v>-0.0537</v>
       </c>
       <c r="L10" s="1">
-        <v>-32.1</v>
+        <v>-36.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0478</v>
+        <v>-0.0537</v>
       </c>
       <c r="N10" s="1">
-        <v>-3.6</v>
+        <v>-14</v>
       </c>
       <c r="O10" s="1">
-        <v>-32.1</v>
+        <v>-37.7</v>
       </c>
       <c r="P10" s="1">
-        <v>-32.1</v>
+        <v>-37.7</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0219</v>
+        <v>0.0217</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
       </c>
       <c r="S10" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0139</v>
+        <v>-0.0063</v>
       </c>
       <c r="U10" s="5">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.05</v>
+        <v>0.0566</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.0549</v>
+        <v>-0.0852</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2519</v>
+        <v>0.2442</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3114</v>
+        <v>0.2885</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2384</v>
+        <v>0.2422</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>852.8</v>
+        <v>862</v>
       </c>
       <c r="D11" s="1">
-        <v>-7.2</v>
+        <v>8.4</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0084</v>
+        <v>0.0098</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,58 +1300,58 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-7.7</v>
+        <v>1.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0089</v>
+        <v>0.0017</v>
       </c>
       <c r="L11" s="1">
-        <v>-7.7</v>
+        <v>1.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0089</v>
+        <v>0.0017</v>
       </c>
       <c r="N11" s="1">
-        <v>-5.6</v>
+        <v>1.6</v>
       </c>
       <c r="O11" s="1">
-        <v>-7.7</v>
+        <v>1.5</v>
       </c>
       <c r="P11" s="1">
-        <v>-7.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0292</v>
+        <v>0.0294</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
       </c>
       <c r="S11" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0084</v>
+        <v>0.0098</v>
       </c>
       <c r="U11" s="5">
-        <v>2.132</v>
+        <v>2.155</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0089</v>
+        <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0037</v>
+        <v>0.0243</v>
       </c>
       <c r="Y11" s="2">
-        <v>-0.0152</v>
+        <v>-0.0046</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1766</v>
+        <v>0.1827</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2735</v>
+        <v>0.2943</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29016.4</v>
+        <v>29320.8</v>
       </c>
       <c r="D12" s="1">
-        <v>-62.3</v>
+        <v>64.2</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-975.39</v>
+        <v>-670.99</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0325</v>
+        <v>-0.0224</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,16 +1395,16 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-229.8</v>
+        <v>76.7</v>
       </c>
       <c r="O12" s="1">
-        <v>-973.89</v>
+        <v>-656.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-973.89</v>
+        <v>-656.69</v>
       </c>
       <c r="Q12" s="2">
-        <v>0.9937</v>
+        <v>1</v>
       </c>
       <c r="R12" t="str">
         <v/>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>673.6</v>
+        <v>678.6</v>
       </c>
       <c r="D2" s="1">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0044</v>
+        <v>0.003</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-37.5</v>
+        <v>-32.5</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0527</v>
+        <v>-0.0457</v>
       </c>
       <c r="L2" s="1">
-        <v>-37.5</v>
+        <v>-32.5</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0527</v>
+        <v>-0.0457</v>
       </c>
       <c r="N2" s="1">
-        <v>-23.6</v>
+        <v>-18.8</v>
       </c>
       <c r="O2" s="1">
-        <v>-23.6</v>
+        <v>-18.8</v>
       </c>
       <c r="P2" s="1">
-        <v>-37.5</v>
+        <v>-32.7</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0232</v>
+        <v>0.0233</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>16</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0044</v>
+        <v>0.003</v>
       </c>
       <c r="U2" s="5">
-        <v>3.368</v>
+        <v>3.393</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0558</v>
+        <v>0.048</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0017</v>
+        <v>0.0092</v>
       </c>
       <c r="Y2" s="2">
-        <v>-0.0184</v>
+        <v>-0.0111</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1493</v>
+        <v>0.1578</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4073</v>
+        <v>0.4178</v>
       </c>
     </row>
     <row r="3">
@@ -648,16 +648,16 @@
         <v>-0.04</v>
       </c>
       <c r="N3" s="1">
-        <v>-9.6</v>
+        <v>-8.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-9.6</v>
+        <v>-9.2</v>
       </c>
       <c r="P3" s="1">
-        <v>-34.5</v>
+        <v>-34.1</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0285</v>
+        <v>0.0284</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>700.7</v>
+        <v>710.6</v>
       </c>
       <c r="D4" s="1">
-        <v>-2.2</v>
+        <v>7.7</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0031</v>
+        <v>0.011</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-36.4</v>
+        <v>-26.5</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0494</v>
+        <v>-0.036</v>
       </c>
       <c r="L4" s="1">
-        <v>-36.4</v>
+        <v>-26.5</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0494</v>
+        <v>-0.036</v>
       </c>
       <c r="N4" s="1">
-        <v>-5.5</v>
+        <v>4.4</v>
       </c>
       <c r="O4" s="1">
-        <v>-5.5</v>
+        <v>4.4</v>
       </c>
       <c r="P4" s="1">
-        <v>-36.4</v>
+        <v>-26.5</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0241</v>
+        <v>0.0244</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>16</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0031</v>
+        <v>0.011</v>
       </c>
       <c r="U4" s="5">
-        <v>0.637</v>
+        <v>0.646</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0518</v>
+        <v>0.0372</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0124</v>
+        <v>0.0016</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0701</v>
+        <v>-0.057</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1749</v>
+        <v>-0.1632</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1066</v>
+        <v>-0.094</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>984.6</v>
+        <v>985</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-6.7</v>
+        <v>-6.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0068</v>
+        <v>-0.0064</v>
       </c>
       <c r="L5" s="1">
-        <v>-6.7</v>
+        <v>-6.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0068</v>
+        <v>-0.0064</v>
       </c>
       <c r="N5" s="1">
-        <v>-6.4</v>
+        <v>-6</v>
       </c>
       <c r="O5" s="1">
-        <v>-6.4</v>
+        <v>-6.2</v>
       </c>
       <c r="P5" s="1">
-        <v>-6.7</v>
+        <v>-6.5</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0339</v>
+        <v>0.0338</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>16</v>
       </c>
       <c r="T5" s="2">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="U5" s="5">
-        <v>4.923</v>
+        <v>4.925</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0069</v>
+        <v>0.0065</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0205</v>
+        <v>0.0209</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0419</v>
+        <v>0.0423</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0897</v>
+        <v>0.0901</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3046</v>
+        <v>0.3051</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>939.8</v>
+        <v>940.5</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0001</v>
+        <v>0.0009</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-33.9</v>
+        <v>-33.2</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0348</v>
+        <v>-0.0341</v>
       </c>
       <c r="L6" s="1">
-        <v>-33.9</v>
+        <v>-33.2</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0348</v>
+        <v>-0.0341</v>
       </c>
       <c r="N6" s="1">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O6" s="1">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="P6" s="1">
-        <v>-35.7</v>
+        <v>-33.3</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0324</v>
+        <v>0.0323</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>16</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0001</v>
+        <v>0.0009</v>
       </c>
       <c r="U6" s="5">
-        <v>9.398</v>
+        <v>9.405</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0361</v>
+        <v>0.0353</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0289</v>
+        <v>-0.0282</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1404</v>
+        <v>-0.1398</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0365</v>
+        <v>0.0373</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2753</v>
+        <v>0.2763</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3026.7</v>
+        <v>3032.1</v>
       </c>
       <c r="D7" s="1">
-        <v>-2.7</v>
+        <v>2.7</v>
       </c>
       <c r="E7" s="2">
-        <v>-0.0009</v>
+        <v>0.0009</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,28 +968,28 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0026</v>
+        <v>0.0044</v>
       </c>
       <c r="L7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0026</v>
+        <v>0.0044</v>
       </c>
       <c r="N7" s="1">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="P7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1042</v>
+        <v>0.104</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>16</v>
       </c>
       <c r="T7" s="2">
-        <v>-0.0009</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.121</v>
+        <v>1.123</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0036</v>
+        <v>0.0054</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0117</v>
+        <v>0.0135</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0145</v>
+        <v>0.0163</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0216</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>809.4</v>
+        <v>817.4</v>
       </c>
       <c r="D8" s="1">
-        <v>-1.2</v>
+        <v>6.8</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0015</v>
+        <v>0.0084</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>22.7</v>
+        <v>30.7</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0289</v>
+        <v>0.039</v>
       </c>
       <c r="L8" s="1">
-        <v>22.7</v>
+        <v>30.7</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0289</v>
+        <v>0.039</v>
       </c>
       <c r="N8" s="1">
-        <v>-23</v>
+        <v>-14.6</v>
       </c>
       <c r="O8" s="1">
-        <v>-23</v>
+        <v>-14.4</v>
       </c>
       <c r="P8" s="1">
-        <v>22.7</v>
+        <v>31.3</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0279</v>
+        <v>0.028</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>16</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0015</v>
+        <v>0.0084</v>
       </c>
       <c r="U8" s="5">
-        <v>4.047</v>
+        <v>4.087</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0971</v>
+        <v>0.1079</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.226</v>
+        <v>0.2381</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3334</v>
+        <v>0.3466</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0523</v>
+        <v>1.0725</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19584.6</v>
+        <v>19658.8</v>
       </c>
       <c r="D9" s="1">
-        <v>-15.4</v>
+        <v>58.8</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0008</v>
+        <v>0.003</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-793.04</v>
+        <v>-718.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0389</v>
+        <v>-0.0353</v>
       </c>
       <c r="L9" s="1">
-        <v>-793.04</v>
+        <v>-718.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0389</v>
+        <v>-0.0353</v>
       </c>
       <c r="N9" s="1">
-        <v>-217</v>
+        <v>-121.8</v>
       </c>
       <c r="O9" s="1">
-        <v>-217</v>
+        <v>-145.6</v>
       </c>
       <c r="P9" s="1">
-        <v>-793.04</v>
+        <v>-721.64</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6742</v>
@@ -1164,28 +1164,28 @@
         <v>16</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0008</v>
+        <v>0.003</v>
       </c>
       <c r="U9" s="5">
-        <v>13.989</v>
+        <v>14.042</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0405</v>
+        <v>0.0365</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0213</v>
+        <v>-0.0176</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0416</v>
+        <v>-0.0379</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0448</v>
+        <v>0.0487</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1645</v>
+        <v>0.1689</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>640.8</v>
+        <v>645.2</v>
       </c>
       <c r="D10" s="1">
-        <v>6.8</v>
+        <v>11.2</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0107</v>
+        <v>0.0177</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-31.3</v>
+        <v>-26.9</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0466</v>
+        <v>-0.04</v>
       </c>
       <c r="L10" s="1">
-        <v>-31.3</v>
+        <v>-26.9</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0466</v>
+        <v>-0.04</v>
       </c>
       <c r="N10" s="1">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="O10" s="1">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="P10" s="1">
-        <v>-31.3</v>
+        <v>-26.9</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0221</v>
@@ -1247,28 +1247,28 @@
         <v>16</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0107</v>
+        <v>0.0177</v>
       </c>
       <c r="U10" s="5">
-        <v>1.602</v>
+        <v>1.613</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0487</v>
+        <v>0.0415</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.0713</v>
+        <v>-0.065</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2535</v>
+        <v>0.2621</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.2982</v>
+        <v>0.3071</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2496</v>
+        <v>0.2581</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>859.2</v>
+        <v>860.4</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0015</v>
+        <v>-0.0001</v>
       </c>
       <c r="L11" s="1">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0015</v>
+        <v>-0.0001</v>
       </c>
       <c r="N11" s="1">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="O11" s="1">
-        <v>-4</v>
+        <v>-2.8</v>
       </c>
       <c r="P11" s="1">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0296</v>
+        <v>0.0295</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,28 +1330,28 @@
         <v>16</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="U11" s="5">
-        <v>2.148</v>
+        <v>2.151</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0014</v>
+        <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0302</v>
+        <v>0.0317</v>
       </c>
       <c r="Y11" s="2">
-        <v>-0.0079</v>
+        <v>-0.0065</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.179</v>
+        <v>0.1806</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2955</v>
+        <v>0.2973</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29047.8</v>
+        <v>29157</v>
       </c>
       <c r="D12" s="1">
-        <v>-20.4</v>
+        <v>88.8</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0007</v>
+        <v>0.0031</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-943.99</v>
+        <v>-834.79</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0315</v>
+        <v>-0.0278</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-285.4</v>
+        <v>-153.5</v>
       </c>
       <c r="O12" s="1">
-        <v>-287.2</v>
+        <v>-178.5</v>
       </c>
       <c r="P12" s="1">
-        <v>-945.79</v>
+        <v>-837.09</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>678.6</v>
+        <v>680.2</v>
       </c>
       <c r="D2" s="1">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.003</v>
+        <v>0.0053</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-32.5</v>
+        <v>-30.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0457</v>
+        <v>-0.0434</v>
       </c>
       <c r="L2" s="1">
-        <v>-32.5</v>
+        <v>-30.9</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0457</v>
+        <v>-0.0434</v>
       </c>
       <c r="N2" s="1">
-        <v>-18.8</v>
+        <v>-18</v>
       </c>
       <c r="O2" s="1">
-        <v>-18.8</v>
+        <v>-16.6</v>
       </c>
       <c r="P2" s="1">
-        <v>-32.7</v>
+        <v>-30.5</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0233</v>
@@ -583,28 +583,28 @@
         <v>16</v>
       </c>
       <c r="T2" s="2">
-        <v>0.003</v>
+        <v>0.0053</v>
       </c>
       <c r="U2" s="5">
-        <v>3.393</v>
+        <v>3.401</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.048</v>
+        <v>0.0456</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0092</v>
+        <v>0.0116</v>
       </c>
       <c r="Y2" s="2">
-        <v>-0.0111</v>
+        <v>-0.0088</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1578</v>
+        <v>0.1605</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4178</v>
+        <v>0.4211</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>828.4</v>
+        <v>827.2</v>
       </c>
       <c r="D3" s="1">
-        <v>-2.4</v>
+        <v>-3.6</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0029</v>
+        <v>-0.0043</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-34.5</v>
+        <v>-35.7</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.04</v>
+        <v>-0.0414</v>
       </c>
       <c r="L3" s="1">
-        <v>-34.5</v>
+        <v>-35.7</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.04</v>
+        <v>-0.0414</v>
       </c>
       <c r="N3" s="1">
-        <v>-8.8</v>
+        <v>-10.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-9.2</v>
+        <v>-10.4</v>
       </c>
       <c r="P3" s="1">
-        <v>-34.1</v>
+        <v>-35.3</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0284</v>
@@ -666,28 +666,28 @@
         <v>16</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0029</v>
+        <v>-0.0043</v>
       </c>
       <c r="U3" s="5">
-        <v>2.071</v>
+        <v>2.068</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0415</v>
+        <v>0.043</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0421</v>
+        <v>-0.0435</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0267</v>
+        <v>0.0252</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0232</v>
+        <v>0.0218</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0753</v>
+        <v>0.0737</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>710.6</v>
+        <v>715</v>
       </c>
       <c r="D4" s="1">
-        <v>7.7</v>
+        <v>12.1</v>
       </c>
       <c r="E4" s="2">
-        <v>0.011</v>
+        <v>0.0172</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-26.5</v>
+        <v>-22.1</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.036</v>
+        <v>-0.03</v>
       </c>
       <c r="L4" s="1">
-        <v>-26.5</v>
+        <v>-22.1</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.036</v>
+        <v>-0.03</v>
       </c>
       <c r="N4" s="1">
-        <v>4.4</v>
+        <v>8.8</v>
       </c>
       <c r="O4" s="1">
-        <v>4.4</v>
+        <v>8.8</v>
       </c>
       <c r="P4" s="1">
-        <v>-26.5</v>
+        <v>-22.1</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0244</v>
+        <v>0.0245</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>16</v>
       </c>
       <c r="T4" s="2">
-        <v>0.011</v>
+        <v>0.0172</v>
       </c>
       <c r="U4" s="5">
-        <v>0.646</v>
+        <v>0.65</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0372</v>
+        <v>0.0308</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0016</v>
+        <v>0.0078</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.057</v>
+        <v>-0.0511</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1632</v>
+        <v>-0.1581</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.094</v>
+        <v>-0.0884</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D5" s="1">
-        <v>0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0004</v>
+        <v>-0.0006</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-6.3</v>
+        <v>-7.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0064</v>
+        <v>-0.0074</v>
       </c>
       <c r="L5" s="1">
-        <v>-6.3</v>
+        <v>-7.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0064</v>
+        <v>-0.0074</v>
       </c>
       <c r="N5" s="1">
-        <v>-6</v>
+        <v>-6.8</v>
       </c>
       <c r="O5" s="1">
-        <v>-6.2</v>
+        <v>-7</v>
       </c>
       <c r="P5" s="1">
-        <v>-6.5</v>
+        <v>-7.3</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0338</v>
@@ -832,28 +832,28 @@
         <v>16</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0004</v>
+        <v>-0.0006</v>
       </c>
       <c r="U5" s="5">
-        <v>4.925</v>
+        <v>4.92</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0065</v>
+        <v>0.0075</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0209</v>
+        <v>0.0199</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0423</v>
+        <v>0.0413</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0901</v>
+        <v>0.089</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3051</v>
+        <v>0.3038</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>940.5</v>
+        <v>940.3</v>
       </c>
       <c r="D6" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0009</v>
+        <v>0.0006</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,19 +885,19 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-33.2</v>
+        <v>-33.4</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0341</v>
+        <v>-0.0343</v>
       </c>
       <c r="L6" s="1">
-        <v>-33.2</v>
+        <v>-33.4</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0341</v>
+        <v>-0.0343</v>
       </c>
       <c r="N6" s="1">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O6" s="1">
         <v>4.1</v>
@@ -915,28 +915,28 @@
         <v>16</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0009</v>
+        <v>0.0006</v>
       </c>
       <c r="U6" s="5">
-        <v>9.405</v>
+        <v>9.403</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0353</v>
+        <v>0.0355</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0282</v>
+        <v>-0.0284</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1398</v>
+        <v>-0.14</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0373</v>
+        <v>0.0371</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2763</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3032.1</v>
+        <v>3029.4</v>
       </c>
       <c r="D7" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>0.0009</v>
+        <v>0</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,25 +968,25 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>13.35</v>
+        <v>10.65</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0044</v>
+        <v>0.0035</v>
       </c>
       <c r="L7" s="1">
-        <v>13.35</v>
+        <v>10.65</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0044</v>
+        <v>0.0035</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="O7" s="1">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="P7" s="1">
-        <v>13.35</v>
+        <v>10.65</v>
       </c>
       <c r="Q7" s="2">
         <v>0.104</v>
@@ -998,10 +998,10 @@
         <v>16</v>
       </c>
       <c r="T7" s="2">
-        <v>0.0009</v>
+        <v>0</v>
       </c>
       <c r="U7" s="5">
-        <v>1.123</v>
+        <v>1.122</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0054</v>
+        <v>0.0045</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0135</v>
+        <v>0.0126</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0163</v>
+        <v>0.0154</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0234</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>817.4</v>
+        <v>809.6</v>
       </c>
       <c r="D8" s="1">
-        <v>6.8</v>
+        <v>-1</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0084</v>
+        <v>-0.0012</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>30.7</v>
+        <v>22.9</v>
       </c>
       <c r="K8" s="2">
-        <v>0.039</v>
+        <v>0.0291</v>
       </c>
       <c r="L8" s="1">
-        <v>30.7</v>
+        <v>22.9</v>
       </c>
       <c r="M8" s="2">
-        <v>0.039</v>
+        <v>0.0291</v>
       </c>
       <c r="N8" s="1">
-        <v>-14.6</v>
+        <v>-23</v>
       </c>
       <c r="O8" s="1">
-        <v>-14.4</v>
+        <v>-22.8</v>
       </c>
       <c r="P8" s="1">
-        <v>31.3</v>
+        <v>22.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.028</v>
+        <v>0.0278</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>16</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0084</v>
+        <v>-0.0012</v>
       </c>
       <c r="U8" s="5">
-        <v>4.087</v>
+        <v>4.048</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1079</v>
+        <v>0.0973</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2381</v>
+        <v>0.2263</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3466</v>
+        <v>0.3338</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0725</v>
+        <v>1.0528</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19658.8</v>
+        <v>19651.8</v>
       </c>
       <c r="D9" s="1">
-        <v>58.8</v>
+        <v>51.8</v>
       </c>
       <c r="E9" s="2">
-        <v>0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-718.84</v>
+        <v>-725.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0353</v>
+        <v>-0.0356</v>
       </c>
       <c r="L9" s="1">
-        <v>-718.84</v>
+        <v>-725.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0353</v>
+        <v>-0.0356</v>
       </c>
       <c r="N9" s="1">
-        <v>-121.8</v>
+        <v>-137.2</v>
       </c>
       <c r="O9" s="1">
-        <v>-145.6</v>
+        <v>-149.8</v>
       </c>
       <c r="P9" s="1">
-        <v>-721.64</v>
+        <v>-725.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6742</v>
+        <v>0.6743</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>16</v>
       </c>
       <c r="T9" s="2">
-        <v>0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="U9" s="5">
-        <v>14.042</v>
+        <v>14.037</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0365</v>
+        <v>0.0369</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0176</v>
+        <v>-0.0179</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0379</v>
+        <v>-0.0383</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0487</v>
+        <v>0.0484</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1689</v>
+        <v>0.1685</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>645.2</v>
+        <v>644.4</v>
       </c>
       <c r="D10" s="1">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0177</v>
+        <v>0.0164</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-26.9</v>
+        <v>-27.7</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.04</v>
+        <v>-0.0412</v>
       </c>
       <c r="L10" s="1">
-        <v>-26.9</v>
+        <v>-27.7</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.04</v>
+        <v>-0.0412</v>
       </c>
       <c r="N10" s="1">
-        <v>10</v>
+        <v>9.2</v>
       </c>
       <c r="O10" s="1">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="P10" s="1">
-        <v>-26.9</v>
+        <v>-27.3</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0221</v>
@@ -1247,28 +1247,28 @@
         <v>16</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0177</v>
+        <v>0.0164</v>
       </c>
       <c r="U10" s="5">
-        <v>1.613</v>
+        <v>1.611</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0415</v>
+        <v>0.0428</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.065</v>
+        <v>-0.0661</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2621</v>
+        <v>0.2605</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3071</v>
+        <v>0.3055</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2581</v>
+        <v>0.2566</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>860.4</v>
+        <v>860</v>
       </c>
       <c r="D11" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0001</v>
+        <v>-0.0006</v>
       </c>
       <c r="L11" s="1">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0001</v>
+        <v>-0.0006</v>
       </c>
       <c r="N11" s="1">
-        <v>-2</v>
+        <v>-2.4</v>
       </c>
       <c r="O11" s="1">
-        <v>-2.8</v>
+        <v>-2.4</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0295</v>
@@ -1330,28 +1330,28 @@
         <v>16</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="U11" s="5">
-        <v>2.151</v>
+        <v>2.15</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v/>
+        <v>0.0005</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0317</v>
+        <v>0.0312</v>
       </c>
       <c r="Y11" s="2">
-        <v>-0.0065</v>
+        <v>-0.0069</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1806</v>
+        <v>0.18</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2973</v>
+        <v>0.2967</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29157</v>
+        <v>29141.9</v>
       </c>
       <c r="D12" s="1">
-        <v>88.8</v>
+        <v>73.7</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0031</v>
+        <v>0.0025</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-834.79</v>
+        <v>-849.89</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0278</v>
+        <v>-0.0283</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-153.5</v>
+        <v>-178.9</v>
       </c>
       <c r="O12" s="1">
-        <v>-178.5</v>
+        <v>-189.2</v>
       </c>
       <c r="P12" s="1">
-        <v>-837.09</v>
+        <v>-847.79</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>680.2</v>
+        <v>671.8</v>
       </c>
       <c r="D2" s="1">
-        <v>3.6</v>
+        <v>-4.8</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0053</v>
+        <v>-0.0071</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-30.9</v>
+        <v>-39.3</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0434</v>
+        <v>-0.0553</v>
       </c>
       <c r="L2" s="1">
-        <v>-30.9</v>
+        <v>-39.3</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0434</v>
+        <v>-0.0553</v>
       </c>
       <c r="N2" s="1">
-        <v>-18</v>
+        <v>-25.4</v>
       </c>
       <c r="O2" s="1">
-        <v>-16.6</v>
+        <v>-25.4</v>
       </c>
       <c r="P2" s="1">
-        <v>-30.5</v>
+        <v>-39.3</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0233</v>
+        <v>0.0231</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>16</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0053</v>
+        <v>-0.0071</v>
       </c>
       <c r="U2" s="5">
-        <v>3.401</v>
+        <v>3.359</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0456</v>
+        <v>0.0586</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0116</v>
+        <v>-0.0009</v>
       </c>
       <c r="Y2" s="2">
-        <v>-0.0088</v>
+        <v>-0.021</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1605</v>
+        <v>0.1462</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4211</v>
+        <v>0.4036</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>827.2</v>
+        <v>829.2</v>
       </c>
       <c r="D3" s="1">
-        <v>-3.6</v>
+        <v>-1.6</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0043</v>
+        <v>-0.0019</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-35.7</v>
+        <v>-33.7</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0414</v>
+        <v>-0.0391</v>
       </c>
       <c r="L3" s="1">
-        <v>-35.7</v>
+        <v>-33.7</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0414</v>
+        <v>-0.0391</v>
       </c>
       <c r="N3" s="1">
-        <v>-10.8</v>
+        <v>-8.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-10.4</v>
+        <v>-8.8</v>
       </c>
       <c r="P3" s="1">
-        <v>-35.3</v>
+        <v>-33.7</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0284</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>16</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0043</v>
+        <v>-0.0019</v>
       </c>
       <c r="U3" s="5">
-        <v>2.068</v>
+        <v>2.073</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.043</v>
+        <v>0.0405</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0435</v>
+        <v>-0.0412</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0252</v>
+        <v>0.0277</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0218</v>
+        <v>0.0242</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0737</v>
+        <v>0.0763</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>715</v>
+        <v>712.8</v>
       </c>
       <c r="D4" s="1">
-        <v>12.1</v>
+        <v>9.9</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0172</v>
+        <v>0.0141</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-22.1</v>
+        <v>-24.3</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.03</v>
+        <v>-0.033</v>
       </c>
       <c r="L4" s="1">
-        <v>-22.1</v>
+        <v>-24.3</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.03</v>
+        <v>-0.033</v>
       </c>
       <c r="N4" s="1">
-        <v>8.8</v>
+        <v>6.6</v>
       </c>
       <c r="O4" s="1">
-        <v>8.8</v>
+        <v>6.6</v>
       </c>
       <c r="P4" s="1">
-        <v>-22.1</v>
+        <v>-24.3</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0245</v>
@@ -749,28 +749,28 @@
         <v>16</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0172</v>
+        <v>0.0141</v>
       </c>
       <c r="U4" s="5">
-        <v>0.65</v>
+        <v>0.648</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0308</v>
+        <v>0.034</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0078</v>
+        <v>0.0047</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0511</v>
+        <v>-0.0541</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1581</v>
+        <v>-0.1606</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0884</v>
+        <v>-0.0912</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>984</v>
+        <v>973.6</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.6</v>
+        <v>-11</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0006</v>
+        <v>-0.0112</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-7.3</v>
+        <v>-17.7</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0074</v>
+        <v>-0.0179</v>
       </c>
       <c r="L5" s="1">
-        <v>-7.3</v>
+        <v>-17.7</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0074</v>
+        <v>-0.0179</v>
       </c>
       <c r="N5" s="1">
-        <v>-6.8</v>
+        <v>-17.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-7</v>
+        <v>-17.4</v>
       </c>
       <c r="P5" s="1">
-        <v>-7.3</v>
+        <v>-17.7</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0338</v>
+        <v>0.0335</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>16</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0006</v>
+        <v>-0.0112</v>
       </c>
       <c r="U5" s="5">
-        <v>4.92</v>
+        <v>4.868</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0075</v>
+        <v>0.0183</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0199</v>
+        <v>0.0091</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0413</v>
+        <v>0.0303</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.089</v>
+        <v>0.0775</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3038</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>940.3</v>
+        <v>934.4</v>
       </c>
       <c r="D6" s="1">
-        <v>0.6</v>
+        <v>-5.3</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0006</v>
+        <v>-0.0056</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-33.4</v>
+        <v>-39.3</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0343</v>
+        <v>-0.0404</v>
       </c>
       <c r="L6" s="1">
-        <v>-33.4</v>
+        <v>-39.3</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0343</v>
+        <v>-0.0404</v>
       </c>
       <c r="N6" s="1">
-        <v>4</v>
+        <v>-1.9</v>
       </c>
       <c r="O6" s="1">
-        <v>4.1</v>
+        <v>-1.9</v>
       </c>
       <c r="P6" s="1">
-        <v>-33.3</v>
+        <v>-39.3</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0323</v>
+        <v>0.0321</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>16</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0006</v>
+        <v>-0.0056</v>
       </c>
       <c r="U6" s="5">
-        <v>9.403</v>
+        <v>9.344</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0355</v>
+        <v>0.0421</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0284</v>
+        <v>-0.0345</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.14</v>
+        <v>-0.1453</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0371</v>
+        <v>0.0306</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.276</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="7">
@@ -947,49 +947,49 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3029.4</v>
+        <v>3032.1</v>
       </c>
       <c r="D7" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.0009</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v/>
+      </c>
+      <c r="H7" s="1">
+        <v/>
+      </c>
+      <c r="I7" s="2">
+        <v/>
+      </c>
+      <c r="J7" s="1">
+        <v>13.35</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.0044</v>
+      </c>
+      <c r="L7" s="1">
+        <v>13.35</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.0044</v>
+      </c>
+      <c r="N7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="2">
+      <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="2">
-        <v/>
-      </c>
-      <c r="H7" s="1">
-        <v/>
-      </c>
-      <c r="I7" s="2">
-        <v/>
-      </c>
-      <c r="J7" s="1">
-        <v>10.65</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.0035</v>
-      </c>
-      <c r="L7" s="1">
-        <v>10.65</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.0035</v>
-      </c>
-      <c r="N7" s="1">
-        <v>-2.7</v>
-      </c>
-      <c r="O7" s="1">
-        <v>-2.7</v>
-      </c>
       <c r="P7" s="1">
-        <v>10.65</v>
+        <v>13.35</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.104</v>
+        <v>0.1042</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>16</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.122</v>
+        <v>1.123</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0045</v>
+        <v>0.0054</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0126</v>
+        <v>0.0135</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0154</v>
+        <v>0.0163</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0225</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>809.6</v>
+        <v>792.8</v>
       </c>
       <c r="D8" s="1">
-        <v>-1</v>
+        <v>-17.8</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0012</v>
+        <v>-0.022</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0291</v>
+        <v>0.0078</v>
       </c>
       <c r="L8" s="1">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0291</v>
+        <v>0.0078</v>
       </c>
       <c r="N8" s="1">
-        <v>-23</v>
+        <v>-39.6</v>
       </c>
       <c r="O8" s="1">
-        <v>-22.8</v>
+        <v>-39.6</v>
       </c>
       <c r="P8" s="1">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0278</v>
+        <v>0.0272</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>16</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0012</v>
+        <v>-0.022</v>
       </c>
       <c r="U8" s="5">
-        <v>4.048</v>
+        <v>3.964</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0973</v>
+        <v>0.0746</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2263</v>
+        <v>0.2008</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3338</v>
+        <v>0.3061</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0528</v>
+        <v>1.0102</v>
       </c>
     </row>
     <row r="9">
@@ -1146,7 +1146,7 @@
         <v>-0.0356</v>
       </c>
       <c r="N9" s="1">
-        <v>-137.2</v>
+        <v>-149.8</v>
       </c>
       <c r="O9" s="1">
         <v>-149.8</v>
@@ -1155,7 +1155,7 @@
         <v>-725.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6743</v>
+        <v>0.6752</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>644.4</v>
+        <v>647.2</v>
       </c>
       <c r="D10" s="1">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0164</v>
+        <v>0.0208</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-27.7</v>
+        <v>-24.9</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0412</v>
+        <v>-0.0371</v>
       </c>
       <c r="L10" s="1">
-        <v>-27.7</v>
+        <v>-24.9</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0412</v>
+        <v>-0.0371</v>
       </c>
       <c r="N10" s="1">
-        <v>9.2</v>
+        <v>12</v>
       </c>
       <c r="O10" s="1">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="P10" s="1">
-        <v>-27.3</v>
+        <v>-24.9</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0221</v>
+        <v>0.0222</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>16</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0164</v>
+        <v>0.0208</v>
       </c>
       <c r="U10" s="5">
-        <v>1.611</v>
+        <v>1.618</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0428</v>
+        <v>0.0383</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.0661</v>
+        <v>-0.0621</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2605</v>
+        <v>0.266</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3055</v>
+        <v>0.3111</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2566</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>860</v>
+        <v>859.6</v>
       </c>
       <c r="D11" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0006</v>
+        <v>-0.001</v>
       </c>
       <c r="L11" s="1">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0006</v>
+        <v>-0.001</v>
       </c>
       <c r="N11" s="1">
-        <v>-2.4</v>
+        <v>-3.6</v>
       </c>
       <c r="O11" s="1">
-        <v>-2.4</v>
+        <v>-3.6</v>
       </c>
       <c r="P11" s="1">
-        <v>0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0295</v>
@@ -1330,28 +1330,28 @@
         <v>16</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="U11" s="5">
-        <v>2.15</v>
+        <v>2.149</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0312</v>
+        <v>0.0307</v>
       </c>
       <c r="Y11" s="2">
-        <v>-0.0069</v>
+        <v>-0.0074</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.18</v>
+        <v>0.1795</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2967</v>
+        <v>0.2961</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29141.9</v>
+        <v>29105.3</v>
       </c>
       <c r="D12" s="1">
-        <v>73.7</v>
+        <v>37.1</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-849.89</v>
+        <v>-886.49</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0283</v>
+        <v>-0.0296</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-178.9</v>
+        <v>-227.9</v>
       </c>
       <c r="O12" s="1">
-        <v>-189.2</v>
+        <v>-227.9</v>
       </c>
       <c r="P12" s="1">
-        <v>-847.79</v>
+        <v>-886.49</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>671.6</v>
+        <v>675</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.2</v>
+        <v>3.2</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0003</v>
+        <v>0.0048</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-39.5</v>
+        <v>-36.1</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0555</v>
+        <v>-0.0508</v>
       </c>
       <c r="L2" s="1">
-        <v>-39.5</v>
+        <v>-36.1</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0555</v>
+        <v>-0.0508</v>
       </c>
       <c r="N2" s="1">
-        <v>-25.6</v>
+        <v>-22.4</v>
       </c>
       <c r="O2" s="1">
-        <v>-25.6</v>
+        <v>-22.4</v>
       </c>
       <c r="P2" s="1">
-        <v>-39.5</v>
+        <v>-36.3</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.023</v>
+        <v>0.0231</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>17</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0003</v>
+        <v>0.0048</v>
       </c>
       <c r="U2" s="5">
-        <v>3.358</v>
+        <v>3.375</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.059</v>
+        <v>0.0536</v>
       </c>
       <c r="X2" s="2">
-        <v>-0.0012</v>
+        <v>0.0039</v>
       </c>
       <c r="Y2" s="2">
-        <v>-0.0213</v>
+        <v>-0.0163</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1382</v>
+        <v>0.1439</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4031</v>
+        <v>0.4102</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>826.8</v>
+        <v>816</v>
       </c>
       <c r="D3" s="1">
-        <v>-2.4</v>
+        <v>-13.2</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0029</v>
+        <v>-0.0159</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-36.1</v>
+        <v>-46.9</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0418</v>
+        <v>-0.0544</v>
       </c>
       <c r="L3" s="1">
-        <v>-36.1</v>
+        <v>-46.9</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0418</v>
+        <v>-0.0544</v>
       </c>
       <c r="N3" s="1">
-        <v>-11.2</v>
+        <v>-22.4</v>
       </c>
       <c r="O3" s="1">
-        <v>-11.2</v>
+        <v>-23.2</v>
       </c>
       <c r="P3" s="1">
-        <v>-36.1</v>
+        <v>-48.1</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0284</v>
+        <v>0.0279</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>17</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0029</v>
+        <v>-0.0159</v>
       </c>
       <c r="U3" s="5">
-        <v>2.067</v>
+        <v>2.04</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0435</v>
+        <v>0.0574</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.044</v>
+        <v>-0.0565</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0248</v>
+        <v>0.0114</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0477</v>
+        <v>0.034</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0732</v>
+        <v>0.0592</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>712.8</v>
+        <v>738.1</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>0.0355</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-24.3</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.033</v>
+        <v>0.0014</v>
       </c>
       <c r="L4" s="1">
-        <v>-24.3</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.033</v>
+        <v>0.0014</v>
       </c>
       <c r="N4" s="1">
-        <v>6.6</v>
+        <v>31.9</v>
       </c>
       <c r="O4" s="1">
-        <v>7.7</v>
+        <v>30.8</v>
       </c>
       <c r="P4" s="1">
-        <v>-23.2</v>
+        <v>-0.1</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0245</v>
+        <v>0.0252</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>17</v>
       </c>
       <c r="T4" s="2">
-        <v>0</v>
+        <v>0.0355</v>
       </c>
       <c r="U4" s="5">
-        <v>0.648</v>
+        <v>0.671</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.034</v>
+        <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0047</v>
+        <v>0.0404</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.054</v>
+        <v>-0.0204</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.166</v>
+        <v>-0.1364</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0912</v>
+        <v>-0.0589</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>973.4</v>
+        <v>987.6</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.2</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0002</v>
+        <v>0.0144</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-17.9</v>
+        <v>-3.7</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0181</v>
+        <v>-0.0037</v>
       </c>
       <c r="L5" s="1">
-        <v>-17.9</v>
+        <v>-3.7</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0181</v>
+        <v>-0.0037</v>
       </c>
       <c r="N5" s="1">
-        <v>-17.6</v>
+        <v>-3.6</v>
       </c>
       <c r="O5" s="1">
-        <v>-17.6</v>
+        <v>-3.6</v>
       </c>
       <c r="P5" s="1">
-        <v>-17.9</v>
+        <v>-3.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0334</v>
+        <v>0.0337</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>17</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0002</v>
+        <v>0.0144</v>
       </c>
       <c r="U5" s="5">
-        <v>4.867</v>
+        <v>4.938</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0185</v>
+        <v>0.0038</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0089</v>
+        <v>0.0236</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0301</v>
+        <v>0.0451</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0654</v>
+        <v>0.0809</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2897</v>
+        <v>0.3085</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>930</v>
+        <v>940.7</v>
       </c>
       <c r="D6" s="1">
-        <v>-4.4</v>
+        <v>6.3</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0047</v>
+        <v>0.0067</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-43.7</v>
+        <v>-33</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0449</v>
+        <v>-0.0339</v>
       </c>
       <c r="L6" s="1">
-        <v>-43.7</v>
+        <v>-33</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0449</v>
+        <v>-0.0339</v>
       </c>
       <c r="N6" s="1">
-        <v>-6.3</v>
+        <v>4.4</v>
       </c>
       <c r="O6" s="1">
-        <v>-6.3</v>
+        <v>4.2</v>
       </c>
       <c r="P6" s="1">
-        <v>-43.7</v>
+        <v>-33.2</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0319</v>
+        <v>0.0321</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>17</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0047</v>
+        <v>0.0067</v>
       </c>
       <c r="U6" s="5">
-        <v>9.3</v>
+        <v>9.407</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.047</v>
+        <v>0.0351</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.039</v>
+        <v>-0.028</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1493</v>
+        <v>-0.1395</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0152</v>
+        <v>0.0269</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.262</v>
+        <v>0.2765</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3032.1</v>
+        <v>3034.8</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,28 +968,28 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>13.35</v>
+        <v>16.05</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0044</v>
+        <v>0.0053</v>
       </c>
       <c r="L7" s="1">
-        <v>13.35</v>
+        <v>16.05</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0044</v>
+        <v>0.0053</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P7" s="1">
-        <v>13.35</v>
+        <v>16.05</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.104</v>
+        <v>0.1037</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>17</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.123</v>
+        <v>1.124</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0054</v>
+        <v>0.0063</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0135</v>
+        <v>0.0144</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0154</v>
+        <v>0.0163</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0234</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>796.6</v>
+        <v>814.4</v>
       </c>
       <c r="D8" s="1">
-        <v>3.8</v>
+        <v>21.6</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0048</v>
+        <v>0.0272</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>9.9</v>
+        <v>27.7</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0126</v>
+        <v>0.0352</v>
       </c>
       <c r="L8" s="1">
-        <v>9.9</v>
+        <v>27.7</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0126</v>
+        <v>0.0352</v>
       </c>
       <c r="N8" s="1">
-        <v>-35.8</v>
+        <v>-18.2</v>
       </c>
       <c r="O8" s="1">
-        <v>-35.8</v>
+        <v>-18.4</v>
       </c>
       <c r="P8" s="1">
-        <v>9.9</v>
+        <v>27.3</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0273</v>
+        <v>0.0278</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>17</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0048</v>
+        <v>0.0272</v>
       </c>
       <c r="U8" s="5">
-        <v>3.983</v>
+        <v>4.072</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0797</v>
+        <v>0.1038</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2066</v>
+        <v>0.2335</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2961</v>
+        <v>0.325</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0197</v>
+        <v>1.0649</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19681.2</v>
+        <v>19742.8</v>
       </c>
       <c r="D9" s="1">
-        <v>29.4</v>
+        <v>91</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0015</v>
+        <v>0.0046</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-696.44</v>
+        <v>-634.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0342</v>
+        <v>-0.0312</v>
       </c>
       <c r="L9" s="1">
-        <v>-696.44</v>
+        <v>-634.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0342</v>
+        <v>-0.0312</v>
       </c>
       <c r="N9" s="1">
-        <v>-120.4</v>
+        <v>-58.8</v>
       </c>
       <c r="O9" s="1">
-        <v>-117.6</v>
+        <v>-60.2</v>
       </c>
       <c r="P9" s="1">
-        <v>-693.64</v>
+        <v>-636.24</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6753</v>
+        <v>0.6744</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>17</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0015</v>
+        <v>0.0046</v>
       </c>
       <c r="U9" s="5">
-        <v>14.058</v>
+        <v>14.102</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0354</v>
+        <v>0.0321</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0164</v>
+        <v>-0.0134</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0369</v>
+        <v>-0.0338</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0491</v>
+        <v>0.0524</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1702</v>
+        <v>0.1739</v>
       </c>
     </row>
     <row r="10">
@@ -1229,16 +1229,16 @@
         <v>-0.0329</v>
       </c>
       <c r="N10" s="1">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="O10" s="1">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="P10" s="1">
-        <v>-22.1</v>
+        <v>-22.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0223</v>
+        <v>0.0222</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D11" s="1">
-        <v>12.4</v>
+        <v>16.4</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0144</v>
+        <v>0.0191</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,19 +1300,19 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0134</v>
+        <v>0.018</v>
       </c>
       <c r="L11" s="1">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0134</v>
+        <v>0.018</v>
       </c>
       <c r="N11" s="1">
-        <v>8.4</v>
+        <v>13.2</v>
       </c>
       <c r="O11" s="1">
         <v>13.2</v>
@@ -1330,10 +1330,10 @@
         <v>17</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0144</v>
+        <v>0.0191</v>
       </c>
       <c r="U11" s="5">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0456</v>
+        <v>0.0504</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0069</v>
+        <v>0.0115</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.179</v>
+        <v>0.1844</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3148</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29146.5</v>
+        <v>29275.4</v>
       </c>
       <c r="D12" s="1">
-        <v>41.2</v>
+        <v>170.1</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0014</v>
+        <v>0.0058</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-845.29</v>
+        <v>-716.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0282</v>
+        <v>-0.0239</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-187.1</v>
+        <v>-58.8</v>
       </c>
       <c r="O12" s="1">
-        <v>-178.4</v>
+        <v>-62.5</v>
       </c>
       <c r="P12" s="1">
-        <v>-836.99</v>
+        <v>-721.09</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -574,7 +574,7 @@
         <v>-53.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0229</v>
+        <v>0.023</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -657,7 +657,7 @@
         <v>-54.9</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0281</v>
+        <v>0.0283</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -740,7 +740,7 @@
         <v>-68.3</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0233</v>
+        <v>0.0234</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -823,7 +823,7 @@
         <v>-41.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0331</v>
+        <v>0.0332</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -906,7 +906,7 @@
         <v>-123.1</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0296</v>
+        <v>0.0298</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -989,7 +989,7 @@
         <v>7.95</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1053</v>
+        <v>0.1059</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1072,7 +1072,7 @@
         <v>-20.7</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0267</v>
+        <v>0.0268</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>-1038.04</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6731</v>
+        <v>0.6767</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1238,7 +1238,7 @@
         <v>-5.3</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0232</v>
+        <v>0.0233</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1321,7 +1321,7 @@
         <v>-24.1</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0291</v>
+        <v>0.0293</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1404,7 +1404,7 @@
         <v>-1421.49</v>
       </c>
       <c r="Q12" s="2">
-        <v>0.9944</v>
+        <v>0.9997</v>
       </c>
       <c r="R12" t="str">
         <v/>

--- a/组合实盘追踪/latest.xlsx
+++ b/组合实盘追踪/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>693</v>
+        <v>698.2</v>
       </c>
       <c r="D2" s="1">
-        <v>5.2</v>
+        <v>10.4</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0076</v>
+        <v>0.0151</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-18.1</v>
+        <v>-12.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0254</v>
+        <v>-0.0181</v>
       </c>
       <c r="L2" s="1">
-        <v>-18.1</v>
+        <v>-12.9</v>
       </c>
       <c r="M2" s="2">
         <v/>
       </c>
       <c r="N2" s="1">
-        <v>31.6</v>
+        <v>36.4</v>
       </c>
       <c r="O2" s="1">
-        <v>16</v>
+        <v>21.6</v>
       </c>
       <c r="P2" s="1">
-        <v>-18.5</v>
+        <v>-12.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0237</v>
+        <v>0.0239</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>27</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0076</v>
+        <v>0.0151</v>
       </c>
       <c r="U2" s="5">
-        <v>3.465</v>
+        <v>3.491</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0263</v>
+        <v>0.0186</v>
       </c>
       <c r="X2" s="2">
-        <v>-0.0065</v>
+        <v>0.0009</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0529</v>
+        <v>0.0608</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1824</v>
+        <v>0.1912</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4266</v>
+        <v>0.4373</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>805.6</v>
+        <v>806</v>
       </c>
       <c r="D3" s="1">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0015</v>
+        <v>-0.001</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,19 +636,19 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-57.3</v>
+        <v>-56.9</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0664</v>
+        <v>-0.0659</v>
       </c>
       <c r="L3" s="1">
-        <v>-57.3</v>
+        <v>-56.9</v>
       </c>
       <c r="M3" s="2">
         <v/>
       </c>
       <c r="N3" s="1">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="O3" s="1">
         <v>-24.8</v>
@@ -657,7 +657,7 @@
         <v>-56.9</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>27</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0015</v>
+        <v>-0.001</v>
       </c>
       <c r="U3" s="5">
-        <v>2.014</v>
+        <v>2.015</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.071</v>
+        <v>0.0705</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0359</v>
+        <v>-0.0355</v>
       </c>
       <c r="Y3" s="2">
-        <v>-0.1323</v>
+        <v>-0.1319</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0323</v>
+        <v>0.0328</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0198</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>674.3</v>
+        <v>669.9</v>
       </c>
       <c r="D4" s="1">
-        <v>-8.8</v>
+        <v>-13.2</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0129</v>
+        <v>-0.0193</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-62.8</v>
+        <v>-67.2</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0852</v>
+        <v>-0.0912</v>
       </c>
       <c r="L4" s="1">
-        <v>-62.8</v>
+        <v>-67.2</v>
       </c>
       <c r="M4" s="2">
         <v/>
       </c>
       <c r="N4" s="1">
-        <v>-1.1</v>
+        <v>-5.5</v>
       </c>
       <c r="O4" s="1">
-        <v>-27.5</v>
+        <v>-33</v>
       </c>
       <c r="P4" s="1">
-        <v>-61.7</v>
+        <v>-67.2</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0231</v>
+        <v>0.0229</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>27</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0129</v>
+        <v>-0.0193</v>
       </c>
       <c r="U4" s="5">
-        <v>0.613</v>
+        <v>0.609</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.093</v>
+        <v>0.1002</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0554</v>
+        <v>-0.0616</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0754</v>
+        <v>-0.0814</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1881</v>
+        <v>-0.1934</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1498</v>
+        <v>-0.1553</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>983.6</v>
+        <v>982</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0002</v>
+        <v>-0.0018</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-7.7</v>
+        <v>-9.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0078</v>
+        <v>-0.0094</v>
       </c>
       <c r="L5" s="1">
-        <v>-7.7</v>
+        <v>-9.3</v>
       </c>
       <c r="M5" s="2">
         <v/>
       </c>
       <c r="N5" s="1">
-        <v>20</v>
+        <v>18.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-1.2</v>
+        <v>-2.6</v>
       </c>
       <c r="P5" s="1">
-        <v>-7.9</v>
+        <v>-9.3</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0337</v>
+        <v>0.0336</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>27</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0002</v>
+        <v>-0.0018</v>
       </c>
       <c r="U5" s="5">
-        <v>4.918</v>
+        <v>4.91</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0079</v>
+        <v>0.0096</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0082</v>
+        <v>0.0066</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0515</v>
+        <v>0.0498</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0812</v>
+        <v>0.0794</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2964</v>
+        <v>0.2943</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>892.9</v>
+        <v>894.9</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0001</v>
+        <v>0.0024</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-80.8</v>
+        <v>-78.8</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.083</v>
+        <v>-0.0809</v>
       </c>
       <c r="L6" s="1">
-        <v>-80.8</v>
+        <v>-78.8</v>
       </c>
       <c r="M6" s="2">
         <v/>
       </c>
       <c r="N6" s="1">
-        <v>26.9</v>
+        <v>29</v>
       </c>
       <c r="O6" s="1">
-        <v>-46.8</v>
+        <v>-44.8</v>
       </c>
       <c r="P6" s="1">
-        <v>-80.8</v>
+        <v>-78.8</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0306</v>
@@ -915,28 +915,28 @@
         <v>27</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0001</v>
+        <v>0.0024</v>
       </c>
       <c r="U6" s="5">
-        <v>8.929</v>
+        <v>8.949</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0905</v>
+        <v>0.0881</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0654</v>
+        <v>-0.0633</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1734</v>
+        <v>-0.1716</v>
       </c>
       <c r="Z6" s="2">
-        <v>-0.0451</v>
+        <v>-0.043</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.1767</v>
+        <v>0.1794</v>
       </c>
     </row>
     <row r="7">
@@ -947,46 +947,46 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3021.3</v>
+        <v>3026.7</v>
       </c>
       <c r="D7" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.0009</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v/>
+      </c>
+      <c r="H7" s="1">
+        <v/>
+      </c>
+      <c r="I7" s="2">
+        <v/>
+      </c>
+      <c r="J7" s="1">
+        <v>7.95</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.0026</v>
+      </c>
+      <c r="L7" s="1">
+        <v>7.95</v>
+      </c>
+      <c r="M7" s="2">
+        <v/>
+      </c>
+      <c r="N7" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="O7" s="1">
         <v>-2.7</v>
       </c>
-      <c r="E7" s="2">
-        <v>-0.0009</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="2">
-        <v/>
-      </c>
-      <c r="H7" s="1">
-        <v/>
-      </c>
-      <c r="I7" s="2">
-        <v/>
-      </c>
-      <c r="J7" s="1">
-        <v>2.55</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.0008</v>
-      </c>
-      <c r="L7" s="1">
-        <v>2.55</v>
-      </c>
-      <c r="M7" s="2">
-        <v/>
-      </c>
-      <c r="N7" s="1">
-        <v>-2.7</v>
-      </c>
-      <c r="O7" s="1">
-        <v>-8.1</v>
-      </c>
       <c r="P7" s="1">
-        <v>2.55</v>
+        <v>7.95</v>
       </c>
       <c r="Q7" s="2">
         <v>0.1034</v>
@@ -998,10 +998,10 @@
         <v>27</v>
       </c>
       <c r="T7" s="2">
-        <v>-0.0009</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.119</v>
+        <v>1.121</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0072</v>
+        <v>0.009</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0118</v>
+        <v>0.0136</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0161</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>819.2</v>
+        <v>822.2</v>
       </c>
       <c r="D8" s="1">
-        <v>10.2</v>
+        <v>13.2</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0126</v>
+        <v>0.0163</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0413</v>
+        <v>0.0451</v>
       </c>
       <c r="L8" s="1">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="M8" s="2">
         <v/>
       </c>
       <c r="N8" s="1">
-        <v>49.6</v>
+        <v>53</v>
       </c>
       <c r="O8" s="1">
-        <v>7.8</v>
+        <v>11.6</v>
       </c>
       <c r="P8" s="1">
-        <v>31.7</v>
+        <v>35.5</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.028</v>
+        <v>0.0281</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>27</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0126</v>
+        <v>0.0163</v>
       </c>
       <c r="U8" s="5">
-        <v>4.096</v>
+        <v>4.111</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0317</v>
+        <v>0.0355</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2413</v>
+        <v>0.2458</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3128</v>
+        <v>0.3177</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0277</v>
+        <v>1.0352</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19868.8</v>
+        <v>19906.6</v>
       </c>
       <c r="D9" s="1">
-        <v>42</v>
+        <v>79.8</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0021</v>
+        <v>0.004</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-508.84</v>
+        <v>-471.04</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.025</v>
+        <v>-0.0231</v>
       </c>
       <c r="L9" s="1">
-        <v>-508.84</v>
+        <v>-471.04</v>
       </c>
       <c r="M9" s="2">
         <v/>
       </c>
       <c r="N9" s="1">
-        <v>368.2</v>
+        <v>406</v>
       </c>
       <c r="O9" s="1">
-        <v>270.2</v>
+        <v>306.6</v>
       </c>
       <c r="P9" s="1">
-        <v>-507.44</v>
+        <v>-471.04</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6801</v>
+        <v>0.6802</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>27</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0021</v>
+        <v>0.004</v>
       </c>
       <c r="U9" s="5">
-        <v>14.192</v>
+        <v>14.219</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0256</v>
+        <v>0.0236</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0051</v>
+        <v>0.007</v>
       </c>
       <c r="Y9" s="2">
-        <v>0.0064</v>
+        <v>0.0083</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.06</v>
+        <v>0.0621</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1683</v>
+        <v>0.1705</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>606.8</v>
+        <v>608</v>
       </c>
       <c r="D10" s="1">
-        <v>-14</v>
+        <v>-12.8</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0226</v>
+        <v>-0.0206</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-65.3</v>
+        <v>-64.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0972</v>
+        <v>-0.0954</v>
       </c>
       <c r="L10" s="1">
-        <v>-65.3</v>
+        <v>-64.1</v>
       </c>
       <c r="M10" s="2">
         <v/>
       </c>
       <c r="N10" s="1">
-        <v>-59.2</v>
+        <v>-58</v>
       </c>
       <c r="O10" s="1">
-        <v>-27.6</v>
+        <v>-26</v>
       </c>
       <c r="P10" s="1">
-        <v>-65.7</v>
+        <v>-64.1</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0208</v>
@@ -1247,28 +1247,28 @@
         <v>27</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0226</v>
+        <v>-0.0206</v>
       </c>
       <c r="U10" s="5">
-        <v>1.517</v>
+        <v>1.52</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.1074</v>
+        <v>0.1053</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.08</v>
+        <v>-0.0782</v>
       </c>
       <c r="Y10" s="2">
-        <v>-0.0745</v>
+        <v>-0.0726</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.2791</v>
+        <v>0.2816</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.138</v>
+        <v>0.1403</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>850.8</v>
+        <v>851.2</v>
       </c>
       <c r="D11" s="1">
-        <v>-10.4</v>
+        <v>-10</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0121</v>
+        <v>-0.0116</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-9.7</v>
+        <v>-9.3</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0113</v>
+        <v>-0.0108</v>
       </c>
       <c r="L11" s="1">
-        <v>-9.7</v>
+        <v>-9.3</v>
       </c>
       <c r="M11" s="2">
         <v/>
       </c>
       <c r="N11" s="1">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O11" s="1">
-        <v>-8.8</v>
+        <v>-8.4</v>
       </c>
       <c r="P11" s="1">
-        <v>-9.7</v>
+        <v>-9.3</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0291</v>
@@ -1330,28 +1330,28 @@
         <v>27</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0121</v>
+        <v>-0.0116</v>
       </c>
       <c r="U11" s="5">
-        <v>2.127</v>
+        <v>2.128</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0113</v>
+        <v>0.0108</v>
       </c>
       <c r="X11" s="2">
-        <v>-0.0019</v>
+        <v>-0.0014</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0251</v>
+        <v>0.0256</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.116</v>
+        <v>0.1165</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2721</v>
+        <v>0.2727</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29216.3</v>
+        <v>29265.7</v>
       </c>
       <c r="D12" s="1">
-        <v>20.2</v>
+        <v>69.6</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0007</v>
+        <v>0.0024</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-775.49</v>
+        <v>-726.09</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0259</v>
+        <v>-0.0242</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>436.9</v>
+        <v>486.4</v>
       </c>
       <c r="O12" s="1">
-        <v>149.2</v>
+        <v>197.5</v>
       </c>
       <c r="P12" s="1">
-        <v>-774.39</v>
+        <v>-726.09</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>
